--- a/sheets/민요/검수/옹이.xlsx
+++ b/sheets/민요/검수/옹이.xlsx
@@ -4,15 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
-    <sheet name="악보 2" sheetId="4" r:id="rId4"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -21,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -51,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -74,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -97,6 +176,99 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3942,8 +4114,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:U28"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -3966,1182 +4142,1512 @@
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">옹이 — 민요채보-1/옹이.png (1/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-      <c r="N1" s="6"/>
-      <c r="O1" s="6"/>
-      <c r="P1" s="6"/>
-      <c r="Q1" s="6"/>
-      <c r="R1" s="6"/>
-      <c r="S1" s="6"/>
-      <c r="T1" s="6"/>
-      <c r="U1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="N2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="O2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="P2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="Q2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="R2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="S2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="T2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="U2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="5" t="inlineStr">
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">옹이</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+      <c s="8" r="N2"/>
+      <c s="8" r="O2"/>
+      <c s="8" r="P2"/>
+      <c s="8" r="Q2"/>
+      <c s="8" r="R2"/>
+      <c s="8" r="S2"/>
+      <c s="8" r="T2"/>
+      <c s="8" r="U2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">泗
 㴌</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
-      <c r="D3" s="3" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 㳞</t>
         </is>
       </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="F3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 仲</t>
         </is>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 潢</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">냉</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 潢</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南</t>
         </is>
       </c>
-      <c r="Q3" s="2"/>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="Q3" s="28"/>
+      <c r="R3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S3" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="U3" s="2"/>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="U3" s="28"/>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">리</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="D4" s="22" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 沽</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="E4" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="F4" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G4" s="29"/>
+      <c r="H4" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 林仲</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">마</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="J4" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L4" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="N4" s="23" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 汰㳞</t>
-        </is>
-      </c>
-      <c r="O4" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="O4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">슴</t>
         </is>
       </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q4" s="2"/>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="P4" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q4" s="29"/>
+      <c r="R4" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="S4" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="T4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="T4" s="23" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 㳞汰</t>
-        </is>
-      </c>
-      <c r="U4" s="3"/>
-    </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="U4" s="31"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 沽</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">움</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="E5" s="33"/>
+      <c r="F5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G5" s="33"/>
+      <c r="H5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 太黃</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="J5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 潢</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="K5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="L5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
+      <c r="M5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">히</t>
         </is>
       </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="N5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 汰潢</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="O5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
+      <c r="P5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南</t>
         </is>
       </c>
-      <c r="Q5" s="2" t="inlineStr">
+      <c r="Q5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="R5" s="2" t="inlineStr">
+      <c r="R5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南</t>
         </is>
       </c>
-      <c r="S5" s="2" t="inlineStr">
+      <c r="S5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="T5" s="2" t="inlineStr">
+      <c r="T5" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 仲</t>
         </is>
       </c>
-      <c r="U5" s="2"/>
-    </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="U5" s="33"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="28"/>
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="E6" s="2"/>
-      <c r="F6" s="3" t="inlineStr">
+      <c r="E6" s="28"/>
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 㳞</t>
         </is>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">놓</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 黃太</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">달</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="J6" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 南</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="K6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="L6" s="2" t="inlineStr">
+      <c r="L6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 仲太</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
+      <c r="M6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">등</t>
         </is>
       </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="N6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">南
 仲</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
       </c>
-      <c r="P6" s="2" t="inlineStr">
+      <c r="P6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="Q6" s="28"/>
+      <c r="R6" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 林</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
       </c>
-      <c r="T6" s="2" t="inlineStr">
+      <c r="T6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="U6" s="2"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="U6" s="28"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 㳞</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 潢㳞</t>
-        </is>
-      </c>
-      <c r="E7" s="2"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="E7" s="29"/>
+      <c r="F7" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 淋㳞</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">려</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="J7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 仲太</t>
         </is>
       </c>
-      <c r="K7" s="2" t="inlineStr">
+      <c r="K7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
       </c>
-      <c r="L7" s="2" t="inlineStr">
+      <c r="L7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="M7" s="2" t="inlineStr">
+      <c r="M7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="N7" s="2" t="inlineStr">
+      <c r="N7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="O7" s="2" t="inlineStr">
+      <c r="O7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">질</t>
         </is>
       </c>
-      <c r="P7" s="2" t="inlineStr">
+      <c r="P7" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="Q7" s="2"/>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="Q7" s="29"/>
+      <c r="R7" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S7" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="T7" s="3" t="inlineStr">
+      <c r="T7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="U7" s="3"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="U7" s="31"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="33"/>
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="E8" s="33"/>
+      <c r="F8" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 淋</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="G8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">까</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="H8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="J8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="K8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">간</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
+      <c r="L8" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="M8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">돌</t>
         </is>
       </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="N8" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="P8" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 太</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="S8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="U8" s="2"/>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="T8" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U8" s="33"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="28"/>
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="E9" s="28"/>
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G9" s="28"/>
+      <c r="H9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="I9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="J9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="K9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">다</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="L9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
+      <c r="M9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">린</t>
         </is>
       </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="N9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="O9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">놓</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
+      <c r="P9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q9" s="2"/>
-      <c r="R9" s="2" t="inlineStr">
+      <c r="Q9" s="28"/>
+      <c r="R9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S9" s="2" t="inlineStr">
+      <c r="S9" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="T9" s="2"/>
-      <c r="U9" s="2"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="T9" s="24"/>
+      <c r="U9" s="28"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="24"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G10" s="29"/>
+      <c r="H10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="I10" s="29"/>
+      <c r="J10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="K10" s="29"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="29"/>
+      <c r="N10" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">고</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="Q10" s="2"/>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="S10" s="2"/>
-      <c r="T10" s="2"/>
-      <c r="U10" s="2"/>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
-      <c r="M11" s="2"/>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="P10" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="Q10" s="29"/>
+      <c r="R10" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="S10" s="29"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="29"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="24"/>
+      <c r="C11" s="33"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="33"/>
+      <c r="N11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2" t="inlineStr">
+      <c r="O11" s="33"/>
+      <c r="P11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q11" s="2"/>
-      <c r="R11" s="2" t="inlineStr">
+      <c r="Q11" s="33"/>
+      <c r="R11" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="S11" s="2"/>
-      <c r="T11" s="2"/>
-      <c r="U11" s="2"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="2"/>
-      <c r="Q12" s="2"/>
-      <c r="R12" s="2"/>
-      <c r="S12" s="2"/>
-      <c r="T12" s="2"/>
-      <c r="U12" s="2"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="2"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
-      <c r="P13" s="2"/>
-      <c r="Q13" s="2"/>
-      <c r="R13" s="2"/>
-      <c r="S13" s="2"/>
-      <c r="T13" s="2"/>
-      <c r="U13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="2"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
-      <c r="P14" s="2"/>
-      <c r="Q14" s="2"/>
-      <c r="R14" s="2"/>
-      <c r="S14" s="2"/>
-      <c r="T14" s="2"/>
-      <c r="U14" s="2"/>
-    </row>
-  </sheetData>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
-    <col min="3" max="3" width="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">옹이 — 민요채보-1/옹이.png (2/2)</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋
-―</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
+      <c r="S11" s="33"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="33"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="24"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="24"/>
+      <c r="E12" s="28"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="28"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="28"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="28"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="28"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="28"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="28"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="24"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="24"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="29"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="29"/>
+      <c r="R13" s="24"/>
+      <c r="S13" s="29"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="29"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="24"/>
+      <c r="C14" s="33"/>
+      <c r="D14" s="24"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="33"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="33"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="33"/>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B16">
+        <is>
+          <t xml:space="preserve">옹이</t>
+        </is>
+      </c>
+      <c s="8" r="C16"/>
+      <c s="8" r="D16"/>
+      <c s="8" r="E16"/>
+      <c s="8" r="F16"/>
+      <c s="8" r="G16"/>
+      <c s="8" r="H16"/>
+      <c s="8" r="I16"/>
+      <c s="8" r="J16"/>
+      <c s="8" r="K16"/>
+      <c s="8" r="L16"/>
+      <c s="8" r="M16"/>
+      <c s="8" r="N16"/>
+      <c s="8" r="O16"/>
+      <c s="8" r="P16"/>
+      <c s="8" r="Q16"/>
+      <c s="8" r="R16"/>
+      <c s="8" r="S16"/>
+      <c s="8" r="T16"/>
+      <c s="8" r="U16"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="25"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="25"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="25"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="25"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="25"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="25"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="25"/>
+      <c r="S17" s="34"/>
+      <c r="T17" s="23" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">淋
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="U17" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="25"/>
+      <c r="C18" s="35"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="25"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="25"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="25"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="25"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="25"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="25"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 沖汰</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="U18" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="32" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
+    <row r="19" ht="56" customHeight="1">
+      <c r="B19" s="25"/>
+      <c r="C19" s="36"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="36"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="36"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="36"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="36"/>
+      <c r="L19" s="25"/>
+      <c r="M19" s="36"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="36"/>
+      <c r="P19" s="25"/>
+      <c r="Q19" s="36"/>
+      <c r="R19" s="25"/>
+      <c r="S19" s="36"/>
+      <c r="T19" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 林</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="U19" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="32" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+    <row r="20" ht="56" customHeight="1">
+      <c r="B20" s="25"/>
+      <c r="C20" s="34"/>
+      <c r="D20" s="25"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="25"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="25"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="25"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="25"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="25"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="24" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 仲</t>
-        </is>
-      </c>
-      <c r="C6" s="2"/>
-    </row>
-    <row r="7" ht="32" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="U20" s="28"/>
+    </row>
+    <row r="21" ht="56" customHeight="1">
+      <c r="B21" s="25"/>
+      <c r="C21" s="35"/>
+      <c r="D21" s="25"/>
+      <c r="E21" s="35"/>
+      <c r="F21" s="25"/>
+      <c r="G21" s="35"/>
+      <c r="H21" s="25"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="25"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="25"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="25"/>
+      <c r="S21" s="35"/>
+      <c r="T21" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 汰沖</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="U21" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
+    <row r="22" ht="56" customHeight="1">
+      <c r="B22" s="25"/>
+      <c r="C22" s="36"/>
+      <c r="D22" s="25"/>
+      <c r="E22" s="36"/>
+      <c r="F22" s="25"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="25"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="25"/>
+      <c r="K22" s="36"/>
+      <c r="L22" s="25"/>
+      <c r="M22" s="36"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="36"/>
+      <c r="P22" s="25"/>
+      <c r="Q22" s="36"/>
+      <c r="R22" s="25"/>
+      <c r="S22" s="36"/>
+      <c r="T22" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="U22" s="33"/>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="B23" s="25"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="25"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="25"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="25"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="25"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="25"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="25"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="25"/>
+      <c r="S23" s="34"/>
+      <c r="T23" s="22" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 沖汰</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="U23" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">웅</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="32" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
+    <row r="24" ht="56" customHeight="1">
+      <c r="B24" s="25"/>
+      <c r="C24" s="35"/>
+      <c r="D24" s="25"/>
+      <c r="E24" s="35"/>
+      <c r="F24" s="25"/>
+      <c r="G24" s="35"/>
+      <c r="H24" s="25"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="25"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="25"/>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="25"/>
+      <c r="S24" s="35"/>
+      <c r="T24" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 替潢</t>
         </is>
       </c>
-      <c r="C10" s="5" t="inlineStr">
+      <c r="U24" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
+    <row r="25" ht="56" customHeight="1">
+      <c r="B25" s="25"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="25"/>
+      <c r="E25" s="36"/>
+      <c r="F25" s="25"/>
+      <c r="G25" s="36"/>
+      <c r="H25" s="25"/>
+      <c r="I25" s="36"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="36"/>
+      <c r="L25" s="25"/>
+      <c r="M25" s="36"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="36"/>
+      <c r="P25" s="25"/>
+      <c r="Q25" s="36"/>
+      <c r="R25" s="25"/>
+      <c r="S25" s="36"/>
+      <c r="T25" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 汰沖</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="U25" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+    <row r="26" ht="56" customHeight="1">
+      <c r="B26" s="25"/>
+      <c r="C26" s="34"/>
+      <c r="D26" s="25"/>
+      <c r="E26" s="34"/>
+      <c r="F26" s="25"/>
+      <c r="G26" s="34"/>
+      <c r="H26" s="25"/>
+      <c r="I26" s="34"/>
+      <c r="J26" s="25"/>
+      <c r="K26" s="34"/>
+      <c r="L26" s="25"/>
+      <c r="M26" s="34"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="34"/>
+      <c r="P26" s="25"/>
+      <c r="Q26" s="34"/>
+      <c r="R26" s="25"/>
+      <c r="S26" s="34"/>
+      <c r="T26" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C12" s="3"/>
-    </row>
-    <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="U26" s="27"/>
+    </row>
+    <row r="27" ht="56" customHeight="1">
+      <c r="B27" s="25"/>
+      <c r="C27" s="35"/>
+      <c r="D27" s="25"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="25"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="25"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="25"/>
+      <c r="K27" s="35"/>
+      <c r="L27" s="25"/>
+      <c r="M27" s="35"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="35"/>
+      <c r="P27" s="25"/>
+      <c r="Q27" s="35"/>
+      <c r="R27" s="25"/>
+      <c r="S27" s="35"/>
+      <c r="T27" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C13" s="3"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="U27" s="31"/>
+    </row>
+    <row r="28" ht="56" customHeight="1">
+      <c r="B28" s="25"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="25"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="25"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="25"/>
+      <c r="I28" s="36"/>
+      <c r="J28" s="25"/>
+      <c r="K28" s="36"/>
+      <c r="L28" s="25"/>
+      <c r="M28" s="36"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="36"/>
+      <c r="P28" s="25"/>
+      <c r="Q28" s="36"/>
+      <c r="R28" s="25"/>
+      <c r="S28" s="36"/>
+      <c r="T28" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="C14" s="3"/>
+      <c r="U28" s="37"/>
     </row>
   </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:U2"/>
+    <mergeCell ref="B16:U16"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="61"/>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="14" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>
--- a/sheets/민요/검수/옹이.xlsx
+++ b/sheets/민요/검수/옹이.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -584,12 +584,12 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|㳞汰</t>
+          <t xml:space="preserve">–|㳞汰</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㳞汰</t>
         </is>
       </c>
@@ -620,13 +620,13 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢潢|―</t>
+          <t xml:space="preserve">潢潢|–</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I4" s="3"/>
@@ -840,14 +840,14 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△|南|―</t>
+          <t xml:space="preserve">△|南|–</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I11" s="2"/>
@@ -916,14 +916,14 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△|南|―</t>
+          <t xml:space="preserve">△|南|–</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -996,13 +996,13 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△|―林</t>
+          <t xml:space="preserve">△|–林</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-―林</t>
+–林</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1036,12 +1036,12 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|仲</t>
+          <t xml:space="preserve">–|仲</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―太</t>
+          <t xml:space="preserve">–太</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―太</t>
+          <t xml:space="preserve">–太</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1229,12 +1229,12 @@
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢</t>
+          <t xml:space="preserve">–潢</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢</t>
+          <t xml:space="preserve">–潢</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰|㳞</t>
+          <t xml:space="preserve">–汰|㳞</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰
+          <t xml:space="preserve">–汰
 㳞</t>
         </is>
       </c>
@@ -1312,13 +1312,13 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△汰|―潢</t>
+          <t xml:space="preserve">△汰|–潢</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">△汰
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|姑|仲</t>
+          <t xml:space="preserve">–|姑|仲</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑
 仲</t>
         </is>
@@ -1542,14 +1542,14 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">△|南|―</t>
+          <t xml:space="preserve">△|南|–</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
@@ -1587,12 +1587,12 @@
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南潢</t>
+          <t xml:space="preserve">–|南潢</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南潢</t>
         </is>
       </c>
@@ -1623,13 +1623,13 @@
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△潢|―</t>
+          <t xml:space="preserve">△潢|–</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">△潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -1702,13 +1702,13 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△|―南</t>
+          <t xml:space="preserve">△|–南</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="I32" s="2"/>
@@ -1894,12 +1894,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林|仲</t>
+          <t xml:space="preserve">–林|仲</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林
+          <t xml:space="preserve">–林
 仲</t>
         </is>
       </c>
@@ -1974,14 +1974,14 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|黃|―</t>
+          <t xml:space="preserve">–|黃|–</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 黃
-―</t>
+–</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―太</t>
+          <t xml:space="preserve">–太</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―太</t>
+          <t xml:space="preserve">–太</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
@@ -2058,12 +2058,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―仲</t>
+          <t xml:space="preserve">–仲</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―仲</t>
+          <t xml:space="preserve">–仲</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
@@ -2281,13 +2281,13 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△汰|―潢</t>
+          <t xml:space="preserve">△汰|–潢</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">△汰
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2360,13 +2360,13 @@
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△|―㳞</t>
+          <t xml:space="preserve">△|–㳞</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-―㳞</t>
+–㳞</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -2396,12 +2396,12 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―淋|㴌</t>
+          <t xml:space="preserve">–淋|㴌</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―淋
+          <t xml:space="preserve">–淋
 㴌</t>
         </is>
       </c>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―淋|·</t>
+          <t xml:space="preserve">–淋|·</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―淋
+          <t xml:space="preserve">–淋
 ·</t>
         </is>
       </c>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢|淋㳞</t>
+          <t xml:space="preserve">–潢|淋㳞</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢
+          <t xml:space="preserve">–潢
 淋㳞</t>
         </is>
       </c>
@@ -2600,12 +2600,12 @@
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―㳞|汰潢</t>
+          <t xml:space="preserve">–㳞|汰潢</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―㳞
+          <t xml:space="preserve">–㳞
 汰潢</t>
         </is>
       </c>
@@ -2640,12 +2640,12 @@
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰|㳞仲</t>
+          <t xml:space="preserve">–汰|㳞仲</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰
+          <t xml:space="preserve">–汰
 㳞仲</t>
         </is>
       </c>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|⌞</t>
+          <t xml:space="preserve">–|⌞</t>
         </is>
       </c>
       <c r="H60" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ⌞</t>
         </is>
       </c>
@@ -2904,13 +2904,13 @@
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△潢|―</t>
+          <t xml:space="preserve">△潢|–</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">△潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
@@ -2944,13 +2944,13 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">△潢|―</t>
+          <t xml:space="preserve">△潢|–</t>
         </is>
       </c>
       <c r="H64" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">△潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
@@ -2988,13 +2988,13 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋|―淋</t>
+          <t xml:space="preserve">淋|–淋</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-―淋</t>
+–淋</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
@@ -3068,13 +3068,13 @@
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰㳞|―</t>
+          <t xml:space="preserve">汰㳞|–</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
@@ -3152,13 +3152,13 @@
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△|―汰</t>
+          <t xml:space="preserve">△|–汰</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
@@ -3349,12 +3349,12 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|⌞</t>
+          <t xml:space="preserve">–|⌞</t>
         </is>
       </c>
       <c r="H74" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ⌞</t>
         </is>
       </c>
@@ -3460,14 +3460,14 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△|南|―</t>
+          <t xml:space="preserve">△|南|–</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南
-―</t>
+–</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―|南</t>
+          <t xml:space="preserve">–|南</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -3619,13 +3619,13 @@
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△|―汰</t>
+          <t xml:space="preserve">△|–汰</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
@@ -3738,13 +3738,13 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢汰|―㳞</t>
+          <t xml:space="preserve">潢汰|–㳞</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰
-―㳞</t>
+–㳞</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
@@ -3817,12 +3817,12 @@
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I86" s="2"/>
@@ -3852,14 +3852,14 @@
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞汰|△黃|―潢</t>
+          <t xml:space="preserve">㳞汰|△黃|–潢</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰
 △黃
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
         <is>
           <t xml:space="preserve">△
 南
-―</t>
+–</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
@@ -3992,7 +3992,7 @@
       <c r="D3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
@@ -4043,7 +4043,7 @@
         <is>
           <t xml:space="preserve">△
 南
-―</t>
+–</t>
         </is>
       </c>
       <c r="O3" s="11" t="inlineStr">
@@ -4065,7 +4065,7 @@
         <is>
           <t xml:space="preserve">△
 南
-―</t>
+–</t>
         </is>
       </c>
       <c r="S3" s="8" t="inlineStr">
@@ -4084,7 +4084,7 @@
       <c r="A4" s="0"/>
       <c r="B4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南</t>
         </is>
       </c>
@@ -4107,7 +4107,7 @@
       <c r="G4" s="9"/>
       <c r="H4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢
+          <t xml:space="preserve">–潢
 淋㳞</t>
         </is>
       </c>
@@ -4124,7 +4124,7 @@
       <c r="K4" s="9"/>
       <c r="L4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―林
+          <t xml:space="preserve">–林
 仲</t>
         </is>
       </c>
@@ -4135,14 +4135,14 @@
       </c>
       <c r="N4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 南潢</t>
         </is>
       </c>
       <c r="O4" s="9"/>
       <c r="P4" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―潢</t>
+          <t xml:space="preserve">–潢</t>
         </is>
       </c>
       <c r="Q4" s="12" t="inlineStr">
@@ -4152,13 +4152,13 @@
       </c>
       <c r="R4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="S4" s="9"/>
       <c r="T4" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 㳞汰</t>
         </is>
       </c>
@@ -4189,7 +4189,7 @@
       <c r="F5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="G5" s="10" t="inlineStr">
@@ -4199,7 +4199,7 @@
       </c>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―㳞
+          <t xml:space="preserve">–㳞
 汰潢</t>
         </is>
       </c>
@@ -4211,7 +4211,7 @@
       <c r="J5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△汰
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="K5" s="10" t="inlineStr">
@@ -4233,7 +4233,7 @@
       <c r="N5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="O5" s="10" t="inlineStr">
@@ -4243,7 +4243,7 @@
       </c>
       <c r="P5" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰
+          <t xml:space="preserve">–汰
 㳞</t>
         </is>
       </c>
@@ -4256,7 +4256,7 @@
         <is>
           <t xml:space="preserve">△
 南
-―</t>
+–</t>
         </is>
       </c>
       <c r="S5" s="10" t="inlineStr">
@@ -4267,7 +4267,7 @@
       <c r="T5" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="U5" s="13"/>
@@ -4298,7 +4298,7 @@
       <c r="F6" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">△潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="G6" s="11" t="inlineStr">
@@ -4308,7 +4308,7 @@
       </c>
       <c r="H6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―汰
+          <t xml:space="preserve">–汰
 㳞仲</t>
         </is>
       </c>
@@ -4329,9 +4329,9 @@
       </c>
       <c r="L6" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 黃
-―</t>
+–</t>
         </is>
       </c>
       <c r="M6" s="11" t="inlineStr">
@@ -4352,7 +4352,7 @@
       <c r="P6" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△汰
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="Q6" s="8" t="inlineStr">
@@ -4383,7 +4383,7 @@
       <c r="B7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-―汰</t>
+–汰</t>
         </is>
       </c>
       <c r="C7" s="9" t="inlineStr">
@@ -4404,7 +4404,7 @@
       <c r="F7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
-―淋</t>
+–淋</t>
         </is>
       </c>
       <c r="G7" s="9" t="inlineStr">
@@ -4425,13 +4425,13 @@
       <c r="J7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-―㳞</t>
+–㳞</t>
         </is>
       </c>
       <c r="K7" s="9"/>
       <c r="L7" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―太</t>
+          <t xml:space="preserve">–太</t>
         </is>
       </c>
       <c r="M7" s="9" t="inlineStr">
@@ -4442,13 +4442,13 @@
       <c r="N7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-―南</t>
+–南</t>
         </is>
       </c>
       <c r="O7" s="9"/>
       <c r="P7" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 姑
 仲</t>
         </is>
@@ -4461,7 +4461,7 @@
       <c r="R7" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-―林</t>
+–林</t>
         </is>
       </c>
       <c r="S7" s="9" t="inlineStr">
@@ -4491,7 +4491,7 @@
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ⌞</t>
         </is>
       </c>
@@ -4515,7 +4515,7 @@
       <c r="I8" s="10"/>
       <c r="J8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―淋
+          <t xml:space="preserve">–淋
 㴌</t>
         </is>
       </c>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="L8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―仲</t>
+          <t xml:space="preserve">–仲</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr">
@@ -4557,7 +4557,7 @@
       </c>
       <c r="R8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
@@ -4594,7 +4594,7 @@
       <c r="F9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
-―</t>
+–</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -4611,7 +4611,7 @@
       <c r="I9" s="8"/>
       <c r="J9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―淋
+          <t xml:space="preserve">–淋
 ·</t>
         </is>
       </c>
@@ -4644,7 +4644,7 @@
       <c r="Q9" s="8"/>
       <c r="R9" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―太</t>
+          <t xml:space="preserve">–太</t>
         </is>
       </c>
       <c r="S9" s="8" t="inlineStr">
@@ -4664,7 +4664,7 @@
       <c r="B10" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰
-―㳞</t>
+–㳞</t>
         </is>
       </c>
       <c r="C10" s="9" t="inlineStr">
@@ -4692,7 +4692,7 @@
       </c>
       <c r="H10" s="18" t="inlineStr">
         <is>
-          <t xml:space="preserve">―
+          <t xml:space="preserve">–
 ⌞</t>
         </is>
       </c>
@@ -4794,7 +4794,7 @@
       <c r="A12" s="0"/>
       <c r="B12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C12" s="8"/>
@@ -4823,7 +4823,7 @@
         <is>
           <t xml:space="preserve">㳞汰
 △黃
-―潢</t>
+–潢</t>
         </is>
       </c>
       <c r="C13" s="9" t="inlineStr">

--- a/sheets/민요/검수/옹이.xlsx
+++ b/sheets/민요/검수/옹이.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3950,937 +3991,937 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">옹이</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+      <c r="Q2" s="20"/>
+      <c r="R2" s="20"/>
+      <c r="S2" s="20"/>
+      <c r="T2" s="20"/>
+      <c r="U2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="17" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南
 –</t>
         </is>
       </c>
-      <c r="C3" s="8" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
       </c>
-      <c r="D3" s="17" t="inlineStr">
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 –汰</t>
         </is>
       </c>
-      <c r="E3" s="8" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
-      <c r="F3" s="17" t="inlineStr">
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="8" t="inlineStr">
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 潢</t>
         </is>
       </c>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="J3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K3" s="8" t="inlineStr">
+      <c r="K3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
       </c>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南
 ·</t>
         </is>
       </c>
-      <c r="M3" s="8"/>
-      <c r="N3" s="18" t="inlineStr">
+      <c r="M3" s="22"/>
+      <c r="N3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南
 –</t>
         </is>
       </c>
-      <c r="O3" s="11" t="inlineStr">
+      <c r="O3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">냉</t>
         </is>
       </c>
-      <c r="P3" s="17" t="inlineStr">
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q3" s="8" t="inlineStr">
+      <c r="Q3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="R3" s="17" t="inlineStr">
+      <c r="R3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南
 –</t>
         </is>
       </c>
-      <c r="S3" s="8" t="inlineStr">
+      <c r="S3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="T3" s="17" t="inlineStr">
+      <c r="T3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="U3" s="8"/>
+      <c r="U3" s="22"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰</t>
         </is>
       </c>
-      <c r="E4" s="9" t="inlineStr">
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리움</t>
         </is>
       </c>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="F4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="25"/>
+      <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–潢
 淋㳞</t>
         </is>
       </c>
-      <c r="I4" s="9" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사랑</t>
         </is>
       </c>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="J4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="K4" s="25"/>
+      <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–林
 仲</t>
         </is>
       </c>
-      <c r="M4" s="9" t="inlineStr">
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="N4" s="17" t="inlineStr">
+      <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南潢</t>
         </is>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="18" t="inlineStr">
+      <c r="O4" s="25"/>
+      <c r="P4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–潢</t>
         </is>
       </c>
-      <c r="Q4" s="12" t="inlineStr">
+      <c r="Q4" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
       </c>
-      <c r="R4" s="17" t="inlineStr">
+      <c r="R4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S4" s="9"/>
-      <c r="T4" s="17" t="inlineStr">
+      <c r="S4" s="25"/>
+      <c r="T4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㳞汰</t>
         </is>
       </c>
-      <c r="U4" s="9"/>
+      <c r="U4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△潢
 –</t>
         </is>
       </c>
-      <c r="G5" s="10" t="inlineStr">
+      <c r="G5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
       </c>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–㳞
 汰潢</t>
         </is>
       </c>
-      <c r="I5" s="10" t="inlineStr">
+      <c r="I5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
       </c>
-      <c r="J5" s="17" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△汰
 –潢</t>
         </is>
       </c>
-      <c r="K5" s="10" t="inlineStr">
+      <c r="K5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">얼마</t>
         </is>
       </c>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 太黃</t>
         </is>
       </c>
-      <c r="M5" s="10" t="inlineStr">
+      <c r="M5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="N5" s="17" t="inlineStr">
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△潢
 –</t>
         </is>
       </c>
-      <c r="O5" s="10" t="inlineStr">
+      <c r="O5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
       </c>
-      <c r="P5" s="17" t="inlineStr">
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–汰
 㳞</t>
         </is>
       </c>
-      <c r="Q5" s="10" t="inlineStr">
+      <c r="Q5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="R5" s="17" t="inlineStr">
+      <c r="R5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南
 –</t>
         </is>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="T5" s="18" t="inlineStr">
+      <c r="T5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢
 –</t>
         </is>
       </c>
-      <c r="U5" s="13"/>
+      <c r="U5" s="28"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="18" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C6" s="11" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 南南</t>
         </is>
       </c>
-      <c r="E6" s="8" t="inlineStr">
+      <c r="E6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">놓을</t>
         </is>
       </c>
-      <c r="F6" s="18" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△潢
 –</t>
         </is>
       </c>
-      <c r="G6" s="11" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">깜</t>
         </is>
       </c>
-      <c r="H6" s="17" t="inlineStr">
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–汰
 㳞仲</t>
         </is>
       </c>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
       </c>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="8" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L6" s="18" t="inlineStr">
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 黃
 –</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr">
+      <c r="M6" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
       </c>
-      <c r="N6" s="17" t="inlineStr">
+      <c r="N6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O6" s="8" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">히</t>
         </is>
       </c>
-      <c r="P6" s="17" t="inlineStr">
+      <c r="P6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△汰
 –潢</t>
         </is>
       </c>
-      <c r="Q6" s="8" t="inlineStr">
+      <c r="Q6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
       </c>
-      <c r="R6" s="17" t="inlineStr">
+      <c r="R6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S6" s="8" t="inlineStr">
+      <c r="S6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="T6" s="17" t="inlineStr">
+      <c r="T6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 仲</t>
         </is>
       </c>
-      <c r="U6" s="8"/>
+      <c r="U6" s="22"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 –汰</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="D7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">까</t>
         </is>
       </c>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="F7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 –淋</t>
         </is>
       </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="G7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
       </c>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="H7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="I7" s="9" t="inlineStr">
+      <c r="I7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">려</t>
         </is>
       </c>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="J7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 –㳞</t>
         </is>
       </c>
-      <c r="K7" s="9"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="K7" s="25"/>
+      <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–太</t>
         </is>
       </c>
-      <c r="M7" s="9" t="inlineStr">
+      <c r="M7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
       </c>
-      <c r="N7" s="17" t="inlineStr">
+      <c r="N7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 –南</t>
         </is>
       </c>
-      <c r="O7" s="9"/>
-      <c r="P7" s="18" t="inlineStr">
+      <c r="O7" s="25"/>
+      <c r="P7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 姑
 仲</t>
         </is>
       </c>
-      <c r="Q7" s="12" t="inlineStr">
+      <c r="Q7" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">질</t>
         </is>
       </c>
-      <c r="R7" s="17" t="inlineStr">
+      <c r="R7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 –林</t>
         </is>
       </c>
-      <c r="S7" s="9" t="inlineStr">
+      <c r="S7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
       </c>
-      <c r="T7" s="17" t="inlineStr">
+      <c r="T7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="U7" s="9"/>
+      <c r="U7" s="25"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 汰</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">옹이가</t>
         </is>
       </c>
-      <c r="D8" s="18" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ⌞</t>
         </is>
       </c>
-      <c r="E8" s="13"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="28"/>
+      <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="G8" s="10" t="inlineStr">
+      <c r="G8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">달</t>
         </is>
       </c>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="H8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I8" s="10"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="I8" s="27"/>
+      <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋
 㴌</t>
         </is>
       </c>
-      <c r="K8" s="10" t="inlineStr">
+      <c r="K8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">달려</t>
         </is>
       </c>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="L8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–仲</t>
         </is>
       </c>
-      <c r="M8" s="10" t="inlineStr">
+      <c r="M8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
       </c>
-      <c r="N8" s="17" t="inlineStr">
+      <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 仲太</t>
         </is>
       </c>
-      <c r="O8" s="10" t="inlineStr">
+      <c r="O8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">등을</t>
         </is>
       </c>
-      <c r="P8" s="17" t="inlineStr">
+      <c r="P8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="Q8" s="10" t="inlineStr">
+      <c r="Q8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
       </c>
-      <c r="R8" s="17" t="inlineStr">
+      <c r="R8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 仲</t>
         </is>
       </c>
-      <c r="S8" s="10" t="inlineStr">
+      <c r="S8" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
       </c>
-      <c r="T8" s="17" t="inlineStr">
+      <c r="T8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="U8" s="10"/>
+      <c r="U8" s="27"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">된</t>
         </is>
       </c>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="D9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="E9" s="8"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E9" s="22"/>
+      <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
 –</t>
         </is>
       </c>
-      <c r="G9" s="8" t="inlineStr">
+      <c r="G9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">려</t>
         </is>
       </c>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="H9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ⁚</t>
         </is>
       </c>
-      <c r="I9" s="8"/>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="I9" s="22"/>
+      <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋
 ·</t>
         </is>
       </c>
-      <c r="K9" s="8" t="inlineStr">
+      <c r="K9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
       </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M9" s="8"/>
-      <c r="N9" s="18" t="inlineStr">
+      <c r="M9" s="22"/>
+      <c r="N9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="O9" s="11" t="inlineStr">
+      <c r="O9" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
       </c>
-      <c r="P9" s="17" t="inlineStr">
+      <c r="P9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q9" s="8"/>
-      <c r="R9" s="17" t="inlineStr">
+      <c r="Q9" s="22"/>
+      <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–太</t>
         </is>
       </c>
-      <c r="S9" s="8" t="inlineStr">
+      <c r="S9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
       </c>
-      <c r="T9" s="17" t="inlineStr">
+      <c r="T9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="U9" s="8"/>
+      <c r="U9" s="22"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰
 –㳞</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사랑</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="E10" s="9"/>
-      <c r="F10" s="18" t="inlineStr">
+      <c r="E10" s="25"/>
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ⌞</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">가야</t>
         </is>
       </c>
-      <c r="H10" s="18" t="inlineStr">
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ⌞</t>
         </is>
       </c>
-      <c r="I10" s="12"/>
-      <c r="J10" s="18" t="inlineStr">
+      <c r="I10" s="26"/>
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ⌞</t>
         </is>
       </c>
-      <c r="K10" s="12" t="inlineStr">
+      <c r="K10" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
       </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="L10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M10" s="25"/>
+      <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="17" t="inlineStr">
+      <c r="O10" s="25"/>
+      <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="Q10" s="9"/>
-      <c r="R10" s="17" t="inlineStr">
+      <c r="Q10" s="25"/>
+      <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S10" s="9" t="inlineStr">
+      <c r="S10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="T10" s="18" t="inlineStr">
+      <c r="T10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">⌞</t>
         </is>
       </c>
-      <c r="U10" s="12"/>
+      <c r="U10" s="26"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="27" t="inlineStr">
         <is>
           <t xml:space="preserve">때문</t>
         </is>
       </c>
-      <c r="D11" s="17"/>
-      <c r="E11" s="10"/>
-      <c r="F11" s="17"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="17"/>
-      <c r="I11" s="10"/>
-      <c r="J11" s="17"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="18" t="inlineStr">
+      <c r="D11" s="21"/>
+      <c r="E11" s="27"/>
+      <c r="F11" s="21"/>
+      <c r="G11" s="27"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="27"/>
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ⌞</t>
         </is>
       </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="17"/>
-      <c r="O11" s="10"/>
-      <c r="P11" s="17" t="inlineStr">
+      <c r="M11" s="28"/>
+      <c r="N11" s="21"/>
+      <c r="O11" s="27"/>
+      <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="Q11" s="10"/>
-      <c r="R11" s="17" t="inlineStr">
+      <c r="Q11" s="27"/>
+      <c r="R11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 △</t>
         </is>
       </c>
-      <c r="S11" s="10"/>
-      <c r="T11" s="17"/>
-      <c r="U11" s="10"/>
+      <c r="S11" s="27"/>
+      <c r="T11" s="21"/>
+      <c r="U11" s="27"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="17"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="17"/>
-      <c r="M12" s="8"/>
-      <c r="N12" s="17"/>
-      <c r="O12" s="8"/>
-      <c r="P12" s="17"/>
-      <c r="Q12" s="8"/>
-      <c r="R12" s="17"/>
-      <c r="S12" s="8"/>
-      <c r="T12" s="17"/>
-      <c r="U12" s="8"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="21"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="21"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="22"/>
+      <c r="L12" s="21"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="21"/>
+      <c r="O12" s="22"/>
+      <c r="P12" s="21"/>
+      <c r="Q12" s="22"/>
+      <c r="R12" s="21"/>
+      <c r="S12" s="22"/>
+      <c r="T12" s="21"/>
+      <c r="U12" s="22"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰
 △黃
 –潢</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17"/>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="17"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="17"/>
-      <c r="Q13" s="9"/>
-      <c r="R13" s="17"/>
-      <c r="S13" s="9"/>
-      <c r="T13" s="17"/>
-      <c r="U13" s="9"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="25"/>
+      <c r="F13" s="21"/>
+      <c r="G13" s="25"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="25"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="25"/>
+      <c r="L13" s="21"/>
+      <c r="M13" s="25"/>
+      <c r="N13" s="21"/>
+      <c r="O13" s="25"/>
+      <c r="P13" s="21"/>
+      <c r="Q13" s="25"/>
+      <c r="R13" s="21"/>
+      <c r="S13" s="25"/>
+      <c r="T13" s="21"/>
+      <c r="U13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="18" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃汰
 㳞</t>
         </is>
       </c>
-      <c r="C14" s="13" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">운운</t>
         </is>
       </c>
-      <c r="D14" s="17"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17"/>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17"/>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17"/>
-      <c r="M14" s="10"/>
-      <c r="N14" s="17"/>
-      <c r="O14" s="10"/>
-      <c r="P14" s="17"/>
-      <c r="Q14" s="10"/>
-      <c r="R14" s="17"/>
-      <c r="S14" s="10"/>
-      <c r="T14" s="17"/>
-      <c r="U14" s="10"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="27"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="27"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="21"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="21"/>
+      <c r="M14" s="27"/>
+      <c r="N14" s="21"/>
+      <c r="O14" s="27"/>
+      <c r="P14" s="21"/>
+      <c r="Q14" s="27"/>
+      <c r="R14" s="21"/>
+      <c r="S14" s="27"/>
+      <c r="T14" s="21"/>
+      <c r="U14" s="27"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/옹이.xlsx
+++ b/sheets/민요/검수/옹이.xlsx
@@ -3964,32 +3964,32 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="12" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="12" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="20" max="20" width="12" customWidth="1"/>
     <col min="21" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="82.06" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="82.06" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4076,7 +4076,7 @@
         <is>
           <t xml:space="preserve">△
 南
-·</t>
+–</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="U3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="F4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G4" s="25"/>
@@ -4159,7 +4159,7 @@
       </c>
       <c r="J4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K4" s="25"/>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="U4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="U5" s="28"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4419,7 +4419,7 @@
       </c>
       <c r="U6" s="22"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
       </c>
       <c r="U7" s="25"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="H8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="27"/>
@@ -4609,12 +4609,12 @@
       </c>
       <c r="T8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="U8" s="27"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4628,7 +4628,7 @@
       </c>
       <c r="D9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E9" s="22"/>
@@ -4645,7 +4645,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ⁚</t>
         </is>
       </c>
@@ -4653,7 +4653,7 @@
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋
-·</t>
+–</t>
         </is>
       </c>
       <c r="K9" s="22" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="L9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M9" s="22"/>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="P9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q9" s="22"/>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="U9" s="22"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4715,32 +4715,32 @@
       </c>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="E10" s="25"/>
       <c r="F10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-⌞</t>
-        </is>
-      </c>
-      <c r="G10" s="26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가야</t>
-        </is>
-      </c>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
           <t xml:space="preserve">–
 ⌞</t>
         </is>
       </c>
+      <c r="G10" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가야</t>
+        </is>
+      </c>
+      <c r="H10" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+⌞</t>
+        </is>
+      </c>
       <c r="I10" s="26"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ⌞</t>
         </is>
       </c>
@@ -4751,20 +4751,20 @@
       </c>
       <c r="L10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="M10" s="25"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="O10" s="25"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="Q10" s="25"/>
@@ -4785,7 +4785,7 @@
       </c>
       <c r="U10" s="26"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4807,7 +4807,7 @@
       <c r="K11" s="27"/>
       <c r="L11" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ⌞</t>
         </is>
       </c>
@@ -4816,14 +4816,14 @@
       <c r="O11" s="27"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
       <c r="Q11" s="27"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 △</t>
         </is>
       </c>
@@ -4831,7 +4831,7 @@
       <c r="T11" s="21"/>
       <c r="U11" s="27"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       <c r="T12" s="21"/>
       <c r="U12" s="22"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4891,7 +4891,7 @@
       <c r="T13" s="21"/>
       <c r="U13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>

--- a/sheets/민요/검수/옹이.xlsx
+++ b/sheets/민요/검수/옹이.xlsx
@@ -2795,13 +2795,12 @@
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|⁚</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-⁚</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I59" s="2"/>
@@ -4645,8 +4644,7 @@
       </c>
       <c r="H9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-⁚</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I9" s="22"/>

--- a/sheets/민요/검수/옹이.xlsx
+++ b/sheets/민요/검수/옹이.xlsx
@@ -4136,7 +4136,8 @@
       </c>
       <c r="E4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">리움</t>
+          <t xml:space="preserve">리
+움</t>
         </is>
       </c>
       <c r="F4" s="21" t="inlineStr">
@@ -4153,7 +4154,8 @@
       </c>
       <c r="I4" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">사랑</t>
+          <t xml:space="preserve">사
+랑</t>
         </is>
       </c>
       <c r="J4" s="21" t="inlineStr">
@@ -4256,7 +4258,8 @@
       </c>
       <c r="K5" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">얼마</t>
+          <t xml:space="preserve">얼
+마</t>
         </is>
       </c>
       <c r="L5" s="21" t="inlineStr">
@@ -4332,7 +4335,8 @@
       </c>
       <c r="E6" s="22" t="inlineStr">
         <is>
-          <t xml:space="preserve">놓을</t>
+          <t xml:space="preserve">놓
+을</t>
         </is>
       </c>
       <c r="F6" s="23" t="inlineStr">
@@ -4526,7 +4530,9 @@
       </c>
       <c r="C8" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">옹이가</t>
+          <t xml:space="preserve">옹
+이
+가</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
@@ -4561,7 +4567,8 @@
       </c>
       <c r="K8" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">달려</t>
+          <t xml:space="preserve">달
+려</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
@@ -4582,7 +4589,8 @@
       </c>
       <c r="O8" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">등을</t>
+          <t xml:space="preserve">등
+을</t>
         </is>
       </c>
       <c r="P8" s="21" t="inlineStr">
@@ -4708,7 +4716,8 @@
       </c>
       <c r="C10" s="25" t="inlineStr">
         <is>
-          <t xml:space="preserve">사랑</t>
+          <t xml:space="preserve">사
+랑</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -4726,7 +4735,8 @@
       </c>
       <c r="G10" s="26" t="inlineStr">
         <is>
-          <t xml:space="preserve">가야</t>
+          <t xml:space="preserve">가
+야</t>
         </is>
       </c>
       <c r="H10" s="23" t="inlineStr">
@@ -4792,7 +4802,8 @@
       </c>
       <c r="C11" s="27" t="inlineStr">
         <is>
-          <t xml:space="preserve">때문</t>
+          <t xml:space="preserve">때
+문</t>
         </is>
       </c>
       <c r="D11" s="21"/>
@@ -4899,7 +4910,8 @@
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
-          <t xml:space="preserve">운운</t>
+          <t xml:space="preserve">운
+운</t>
         </is>
       </c>
       <c r="D14" s="21"/>

--- a/sheets/민요/검수/옹이.xlsx
+++ b/sheets/민요/검수/옹이.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -4024,7 +4047,7 @@
 –</t>
         </is>
       </c>
-      <c r="C3" s="22" t="inlineStr">
+      <c r="C3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
@@ -4035,7 +4058,7 @@
 –汰</t>
         </is>
       </c>
-      <c r="E3" s="22" t="inlineStr">
+      <c r="E3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
@@ -4045,7 +4068,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G3" s="22" t="inlineStr">
+      <c r="G3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4056,7 +4079,7 @@
 潢</t>
         </is>
       </c>
-      <c r="I3" s="22" t="inlineStr">
+      <c r="I3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
@@ -4066,7 +4089,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K3" s="22" t="inlineStr">
+      <c r="K3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
@@ -4078,7 +4101,7 @@
 –</t>
         </is>
       </c>
-      <c r="M3" s="22"/>
+      <c r="M3" s="29"/>
       <c r="N3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△
@@ -4086,7 +4109,7 @@
 –</t>
         </is>
       </c>
-      <c r="O3" s="24" t="inlineStr">
+      <c r="O3" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">냉</t>
         </is>
@@ -4096,7 +4119,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="Q3" s="22" t="inlineStr">
+      <c r="Q3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4108,7 +4131,7 @@
 –</t>
         </is>
       </c>
-      <c r="S3" s="22" t="inlineStr">
+      <c r="S3" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -4118,7 +4141,7 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="U3" s="22"/>
+      <c r="U3" s="29"/>
     </row>
     <row r="4" ht="82.06" customHeight="1">
       <c r="A4" s="0"/>
@@ -4128,13 +4151,13 @@
 南</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞汰</t>
         </is>
       </c>
-      <c r="E4" s="25" t="inlineStr">
+      <c r="E4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">리
 움</t>
@@ -4145,14 +4168,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="25"/>
+      <c r="G4" s="31"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–潢
 淋㳞</t>
         </is>
       </c>
-      <c r="I4" s="25" t="inlineStr">
+      <c r="I4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">사
 랑</t>
@@ -4163,14 +4186,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K4" s="25"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–林
 仲</t>
         </is>
       </c>
-      <c r="M4" s="25" t="inlineStr">
+      <c r="M4" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
@@ -4181,13 +4204,13 @@
 南潢</t>
         </is>
       </c>
-      <c r="O4" s="25"/>
+      <c r="O4" s="31"/>
       <c r="P4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–潢</t>
         </is>
       </c>
-      <c r="Q4" s="26" t="inlineStr">
+      <c r="Q4" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
@@ -4197,14 +4220,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S4" s="25"/>
+      <c r="S4" s="31"/>
       <c r="T4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㳞汰</t>
         </is>
       </c>
-      <c r="U4" s="25"/>
+      <c r="U4" s="31"/>
     </row>
     <row r="5" ht="82.06" customHeight="1">
       <c r="A5" s="0"/>
@@ -4213,7 +4236,7 @@
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">무</t>
         </is>
@@ -4223,7 +4246,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="27" t="inlineStr">
+      <c r="E5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
@@ -4234,7 +4257,7 @@
 –</t>
         </is>
       </c>
-      <c r="G5" s="27" t="inlineStr">
+      <c r="G5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">디</t>
         </is>
@@ -4245,7 +4268,7 @@
 汰潢</t>
         </is>
       </c>
-      <c r="I5" s="27" t="inlineStr">
+      <c r="I5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">을</t>
         </is>
@@ -4256,7 +4279,7 @@
 –潢</t>
         </is>
       </c>
-      <c r="K5" s="27" t="inlineStr">
+      <c r="K5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">얼
 마</t>
@@ -4268,7 +4291,7 @@
 太黃</t>
         </is>
       </c>
-      <c r="M5" s="27" t="inlineStr">
+      <c r="M5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -4279,7 +4302,7 @@
 –</t>
         </is>
       </c>
-      <c r="O5" s="27" t="inlineStr">
+      <c r="O5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">정</t>
         </is>
@@ -4290,7 +4313,7 @@
 㳞</t>
         </is>
       </c>
-      <c r="Q5" s="27" t="inlineStr">
+      <c r="Q5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4302,7 +4325,7 @@
 –</t>
         </is>
       </c>
-      <c r="S5" s="27" t="inlineStr">
+      <c r="S5" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
@@ -4313,7 +4336,7 @@
 –</t>
         </is>
       </c>
-      <c r="U5" s="28"/>
+      <c r="U5" s="34"/>
     </row>
     <row r="6" ht="82.06" customHeight="1">
       <c r="A6" s="0"/>
@@ -4322,7 +4345,7 @@
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">꿈</t>
         </is>
@@ -4333,7 +4356,7 @@
 南南</t>
         </is>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">놓
 을</t>
@@ -4345,7 +4368,7 @@
 –</t>
         </is>
       </c>
-      <c r="G6" s="24" t="inlineStr">
+      <c r="G6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">깜</t>
         </is>
@@ -4356,7 +4379,7 @@
 㳞仲</t>
         </is>
       </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="I6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">내</t>
         </is>
@@ -4366,7 +4389,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="22" t="inlineStr">
+      <c r="K6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4378,7 +4401,7 @@
 –</t>
         </is>
       </c>
-      <c r="M6" s="24" t="inlineStr">
+      <c r="M6" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">지</t>
         </is>
@@ -4388,7 +4411,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O6" s="22" t="inlineStr">
+      <c r="O6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">히</t>
         </is>
@@ -4399,7 +4422,7 @@
 –潢</t>
         </is>
       </c>
-      <c r="Q6" s="22" t="inlineStr">
+      <c r="Q6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
@@ -4409,7 +4432,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S6" s="22" t="inlineStr">
+      <c r="S6" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4420,7 +4443,7 @@
 仲</t>
         </is>
       </c>
-      <c r="U6" s="22"/>
+      <c r="U6" s="29"/>
     </row>
     <row r="7" ht="82.06" customHeight="1">
       <c r="A7" s="0"/>
@@ -4430,7 +4453,7 @@
 –汰</t>
         </is>
       </c>
-      <c r="C7" s="25" t="inlineStr">
+      <c r="C7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4440,7 +4463,7 @@
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E7" s="25" t="inlineStr">
+      <c r="E7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">까</t>
         </is>
@@ -4451,7 +4474,7 @@
 –淋</t>
         </is>
       </c>
-      <c r="G7" s="25" t="inlineStr">
+      <c r="G7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">음</t>
         </is>
@@ -4461,7 +4484,7 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="I7" s="25" t="inlineStr">
+      <c r="I7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">려</t>
         </is>
@@ -4472,13 +4495,13 @@
 –㳞</t>
         </is>
       </c>
-      <c r="K7" s="25"/>
+      <c r="K7" s="31"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–太</t>
         </is>
       </c>
-      <c r="M7" s="25" t="inlineStr">
+      <c r="M7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">우</t>
         </is>
@@ -4489,7 +4512,7 @@
 –南</t>
         </is>
       </c>
-      <c r="O7" s="25"/>
+      <c r="O7" s="31"/>
       <c r="P7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
@@ -4497,7 +4520,7 @@
 仲</t>
         </is>
       </c>
-      <c r="Q7" s="26" t="inlineStr">
+      <c r="Q7" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">질</t>
         </is>
@@ -4508,7 +4531,7 @@
 –林</t>
         </is>
       </c>
-      <c r="S7" s="25" t="inlineStr">
+      <c r="S7" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
@@ -4518,7 +4541,7 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="U7" s="25"/>
+      <c r="U7" s="31"/>
     </row>
     <row r="8" ht="82.06" customHeight="1">
       <c r="A8" s="0"/>
@@ -4528,7 +4551,7 @@
 汰</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">옹
 이
@@ -4541,14 +4564,14 @@
 ⌞</t>
         </is>
       </c>
-      <c r="E8" s="28"/>
+      <c r="E8" s="34"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="G8" s="27" t="inlineStr">
+      <c r="G8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">달</t>
         </is>
@@ -4558,14 +4581,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="27"/>
+      <c r="I8" s="33"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋
 㴌</t>
         </is>
       </c>
-      <c r="K8" s="27" t="inlineStr">
+      <c r="K8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">달
 려</t>
@@ -4576,7 +4599,7 @@
           <t xml:space="preserve">–仲</t>
         </is>
       </c>
-      <c r="M8" s="27" t="inlineStr">
+      <c r="M8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
@@ -4587,7 +4610,7 @@
 仲太</t>
         </is>
       </c>
-      <c r="O8" s="27" t="inlineStr">
+      <c r="O8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">등
 을</t>
@@ -4598,7 +4621,7 @@
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="Q8" s="27" t="inlineStr">
+      <c r="Q8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">러</t>
         </is>
@@ -4609,7 +4632,7 @@
 仲</t>
         </is>
       </c>
-      <c r="S8" s="27" t="inlineStr">
+      <c r="S8" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">씨</t>
         </is>
@@ -4619,7 +4642,7 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U8" s="27"/>
+      <c r="U8" s="33"/>
     </row>
     <row r="9" ht="82.06" customHeight="1">
       <c r="A9" s="0"/>
@@ -4628,7 +4651,7 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">된</t>
         </is>
@@ -4638,14 +4661,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E9" s="22"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
 –</t>
         </is>
       </c>
-      <c r="G9" s="22" t="inlineStr">
+      <c r="G9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">려</t>
         </is>
@@ -4655,14 +4678,14 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I9" s="22"/>
+      <c r="I9" s="29"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋
 –</t>
         </is>
       </c>
-      <c r="K9" s="22" t="inlineStr">
+      <c r="K9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">가</t>
         </is>
@@ -4672,13 +4695,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M9" s="22"/>
+      <c r="M9" s="29"/>
       <c r="N9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="O9" s="24" t="inlineStr">
+      <c r="O9" s="30" t="inlineStr">
         <is>
           <t xml:space="preserve">들</t>
         </is>
@@ -4688,13 +4711,13 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q9" s="22"/>
+      <c r="Q9" s="29"/>
       <c r="R9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–太</t>
         </is>
       </c>
-      <c r="S9" s="22" t="inlineStr">
+      <c r="S9" s="29" t="inlineStr">
         <is>
           <t xml:space="preserve">하</t>
         </is>
@@ -4704,7 +4727,7 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="U9" s="22"/>
+      <c r="U9" s="29"/>
     </row>
     <row r="10" ht="82.06" customHeight="1">
       <c r="A10" s="0"/>
@@ -4714,7 +4737,7 @@
 –㳞</t>
         </is>
       </c>
-      <c r="C10" s="25" t="inlineStr">
+      <c r="C10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">사
 랑</t>
@@ -4726,14 +4749,14 @@
 △</t>
         </is>
       </c>
-      <c r="E10" s="25"/>
+      <c r="E10" s="31"/>
       <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ⌞</t>
         </is>
       </c>
-      <c r="G10" s="26" t="inlineStr">
+      <c r="G10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">가
 야</t>
@@ -4745,14 +4768,14 @@
 ⌞</t>
         </is>
       </c>
-      <c r="I10" s="26"/>
+      <c r="I10" s="32"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ⌞</t>
         </is>
       </c>
-      <c r="K10" s="26" t="inlineStr">
+      <c r="K10" s="32" t="inlineStr">
         <is>
           <t xml:space="preserve">아</t>
         </is>
@@ -4762,26 +4785,26 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M10" s="25"/>
+      <c r="M10" s="31"/>
       <c r="N10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="O10" s="25"/>
+      <c r="O10" s="31"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q10" s="25"/>
+      <c r="Q10" s="31"/>
       <c r="R10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">仲</t>
         </is>
       </c>
-      <c r="S10" s="25" t="inlineStr">
+      <c r="S10" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
@@ -4791,7 +4814,7 @@
           <t xml:space="preserve">⌞</t>
         </is>
       </c>
-      <c r="U10" s="26"/>
+      <c r="U10" s="32"/>
     </row>
     <row r="11" ht="82.06" customHeight="1">
       <c r="A11" s="0"/>
@@ -4800,45 +4823,45 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="C11" s="27" t="inlineStr">
+      <c r="C11" s="33" t="inlineStr">
         <is>
           <t xml:space="preserve">때
 문</t>
         </is>
       </c>
       <c r="D11" s="21"/>
-      <c r="E11" s="27"/>
+      <c r="E11" s="33"/>
       <c r="F11" s="21"/>
-      <c r="G11" s="27"/>
+      <c r="G11" s="33"/>
       <c r="H11" s="21"/>
-      <c r="I11" s="27"/>
+      <c r="I11" s="33"/>
       <c r="J11" s="21"/>
-      <c r="K11" s="27"/>
+      <c r="K11" s="33"/>
       <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 ⌞</t>
         </is>
       </c>
-      <c r="M11" s="28"/>
+      <c r="M11" s="34"/>
       <c r="N11" s="21"/>
-      <c r="O11" s="27"/>
+      <c r="O11" s="33"/>
       <c r="P11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="Q11" s="27"/>
+      <c r="Q11" s="33"/>
       <c r="R11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="S11" s="27"/>
+      <c r="S11" s="33"/>
       <c r="T11" s="21"/>
-      <c r="U11" s="27"/>
+      <c r="U11" s="33"/>
     </row>
     <row r="12" ht="82.06" customHeight="1">
       <c r="A12" s="0"/>
@@ -4847,25 +4870,25 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C12" s="22"/>
+      <c r="C12" s="29"/>
       <c r="D12" s="21"/>
-      <c r="E12" s="22"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="21"/>
-      <c r="G12" s="22"/>
+      <c r="G12" s="29"/>
       <c r="H12" s="21"/>
-      <c r="I12" s="22"/>
+      <c r="I12" s="29"/>
       <c r="J12" s="21"/>
-      <c r="K12" s="22"/>
+      <c r="K12" s="29"/>
       <c r="L12" s="21"/>
-      <c r="M12" s="22"/>
+      <c r="M12" s="29"/>
       <c r="N12" s="21"/>
-      <c r="O12" s="22"/>
+      <c r="O12" s="29"/>
       <c r="P12" s="21"/>
-      <c r="Q12" s="22"/>
+      <c r="Q12" s="29"/>
       <c r="R12" s="21"/>
-      <c r="S12" s="22"/>
+      <c r="S12" s="29"/>
       <c r="T12" s="21"/>
-      <c r="U12" s="22"/>
+      <c r="U12" s="29"/>
     </row>
     <row r="13" ht="82.06" customHeight="1">
       <c r="A13" s="0"/>
@@ -4876,29 +4899,29 @@
 –潢</t>
         </is>
       </c>
-      <c r="C13" s="25" t="inlineStr">
+      <c r="C13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="D13" s="21"/>
-      <c r="E13" s="25"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="21"/>
-      <c r="G13" s="25"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="21"/>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="21"/>
-      <c r="K13" s="25"/>
+      <c r="K13" s="31"/>
       <c r="L13" s="21"/>
-      <c r="M13" s="25"/>
+      <c r="M13" s="31"/>
       <c r="N13" s="21"/>
-      <c r="O13" s="25"/>
+      <c r="O13" s="31"/>
       <c r="P13" s="21"/>
-      <c r="Q13" s="25"/>
+      <c r="Q13" s="31"/>
       <c r="R13" s="21"/>
-      <c r="S13" s="25"/>
+      <c r="S13" s="31"/>
       <c r="T13" s="21"/>
-      <c r="U13" s="25"/>
+      <c r="U13" s="31"/>
     </row>
     <row r="14" ht="82.06" customHeight="1">
       <c r="A14" s="0"/>
@@ -4908,30 +4931,30 @@
 㳞</t>
         </is>
       </c>
-      <c r="C14" s="28" t="inlineStr">
+      <c r="C14" s="34" t="inlineStr">
         <is>
           <t xml:space="preserve">운
 운</t>
         </is>
       </c>
       <c r="D14" s="21"/>
-      <c r="E14" s="27"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="21"/>
-      <c r="G14" s="27"/>
+      <c r="G14" s="33"/>
       <c r="H14" s="21"/>
-      <c r="I14" s="27"/>
+      <c r="I14" s="33"/>
       <c r="J14" s="21"/>
-      <c r="K14" s="27"/>
+      <c r="K14" s="33"/>
       <c r="L14" s="21"/>
-      <c r="M14" s="27"/>
+      <c r="M14" s="33"/>
       <c r="N14" s="21"/>
-      <c r="O14" s="27"/>
+      <c r="O14" s="33"/>
       <c r="P14" s="21"/>
-      <c r="Q14" s="27"/>
+      <c r="Q14" s="33"/>
       <c r="R14" s="21"/>
-      <c r="S14" s="27"/>
+      <c r="S14" s="33"/>
       <c r="T14" s="21"/>
-      <c r="U14" s="27"/>
+      <c r="U14" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/옹이.xlsx
+++ b/sheets/민요/검수/옹이.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -42,11 +42,6 @@
     </font>
     <font>
       <sz val="24"/>
-      <name val="궁서체"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -155,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -232,31 +227,13 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -349,7 +326,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">87</t>
+          <t xml:space="preserve">84</t>
         </is>
       </c>
     </row>
@@ -361,7 +338,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">15</t>
+          <t xml:space="preserve">10</t>
         </is>
       </c>
     </row>
@@ -385,7 +362,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">중</t>
+          <t xml:space="preserve">상</t>
         </is>
       </c>
     </row>
@@ -395,11 +372,7 @@
           <t xml:space="preserve">확인 필요</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">비고 17%</t>
-        </is>
-      </c>
+      <c r="B12" s="4"/>
     </row>
     <row r="13">
       <c r="A13" s="0"/>
@@ -425,7 +398,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">손으로 그린 12정간 격자(번호 없음), 굵은 선 3칸마다 → 3/4·12로 봄. 10줄 사용. 머리 가운데 "조창건"(사람 이름), 오른쪽 위 "채보 이○○대 26.P." 메모, 왼쪽 위 작은 네모 표시(요성/주법 기호로 추정) 있음. 여러 칸 아래쪽에 닫는 곡선 ")" 모양 기호가 반복되는데 기호표에 없어 가장 비슷한 ⌞로 적고 해당 칸 비고에 표시. AI 재판독 초안.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 손으로 그린 격자(번호 없음), 12정간 굵은 선 3칸마다 → 3/4·12. 오른쪽부터 10줄, 줄1은 전주(가사 없음, 위에 '전주' 글씨). 줄2~9는 8정간까지만 쓰고 끝에 –|△, 줄10만 12정간까지. 칸 안 짧은 가로선은 –로 적음. 머리 '옹이', '조창건', 오른쪽 위 채보 메모, 줄10 왼쪽 여백·위에 작은 메모 있음(생략).</t>
         </is>
       </c>
     </row>
@@ -611,18 +584,22 @@
       <c r="F2" s="2">
         <v>1</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="H2" s="2" t="inlineStr">
+      <c r="H2" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="4"/>
+      <c r="I2" s="3"/>
+      <c r="J2" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">淋 위에 '전주' 글씨(줄 그음)</t>
+        </is>
+      </c>
       <c r="K2" s="2"/>
     </row>
     <row r="3">
@@ -682,23 +659,19 @@
       <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢|–</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢
 –</t>
         </is>
       </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢 두 개 나란히</t>
-        </is>
-      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="4"/>
       <c r="K4" s="2"/>
     </row>
     <row r="5">
@@ -793,18 +766,22 @@
       <c r="F7" s="2">
         <v>2</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I7" s="2"/>
-      <c r="J7" s="4"/>
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I7" s="3"/>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">작은 가로선</t>
+        </is>
+      </c>
       <c r="K7" s="2"/>
     </row>
     <row r="8">
@@ -865,18 +842,18 @@
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌞</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌞</t>
+          <t xml:space="preserve">△</t>
         </is>
       </c>
       <c r="I9" s="3"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">닫는 곡선 ")" 모양</t>
+          <t xml:space="preserve">D 모양, 흘려 쓴 △로 봄</t>
         </is>
       </c>
       <c r="K9" s="2"/>
@@ -904,13 +881,12 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△|南|–</t>
+          <t xml:space="preserve">△南|–</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△
-南
+          <t xml:space="preserve">△南
 –</t>
         </is>
       </c>
@@ -980,13 +956,12 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△|南|–</t>
+          <t xml:space="preserve">△南|–</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△
-南
+          <t xml:space="preserve">△南
 –</t>
         </is>
       </c>
@@ -1100,18 +1075,18 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|仲</t>
+          <t xml:space="preserve">–仲|–太</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-仲</t>
+          <t xml:space="preserve">–仲
+–太</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">씨</t>
+          <t xml:space="preserve">씨하</t>
         </is>
       </c>
       <c r="J15" s="4"/>
@@ -1140,17 +1115,17 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–太</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–太</t>
+          <t xml:space="preserve">仲</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">하</t>
+          <t xml:space="preserve">나</t>
         </is>
       </c>
       <c r="J16" s="4"/>
@@ -1179,19 +1154,16 @@
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I17" s="2"/>
       <c r="J17" s="4"/>
       <c r="K17" s="2"/>
     </row>
@@ -1205,29 +1177,33 @@
         </is>
       </c>
       <c r="C18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D18" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E18" s="2">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F18" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|△</t>
+          <t xml:space="preserve">△|–潢</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-△</t>
-        </is>
-      </c>
-      <c r="I18" s="2"/>
+          <t xml:space="preserve">△
+–潢</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
       <c r="J18" s="4"/>
       <c r="K18" s="2"/>
     </row>
@@ -1247,24 +1223,25 @@
         <v>3</v>
       </c>
       <c r="E19" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F19" s="2">
         <v>1</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">–汰|㳞</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△</t>
+          <t xml:space="preserve">–汰
+㳞</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가</t>
+          <t xml:space="preserve">슴에</t>
         </is>
       </c>
       <c r="J19" s="4"/>
@@ -1286,31 +1263,28 @@
         <v>3</v>
       </c>
       <c r="E20" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F20" s="2">
         <v>1</v>
       </c>
-      <c r="G20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–潢</t>
-        </is>
-      </c>
-      <c r="H20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–潢</t>
-        </is>
-      </c>
-      <c r="I20" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">음</t>
-        </is>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 음/슴?</t>
-        </is>
-      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△汰|–潢</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△汰
+–潢</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">불질</t>
+        </is>
+      </c>
+      <c r="J20" s="4"/>
       <c r="K20" s="2"/>
     </row>
     <row r="21">
@@ -1329,25 +1303,25 @@
         <v>3</v>
       </c>
       <c r="E21" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F21" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–汰|㳞</t>
+          <t xml:space="preserve">–南|仲</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–汰
-㳞</t>
+          <t xml:space="preserve">–南
+仲</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">에</t>
+          <t xml:space="preserve">러놓</t>
         </is>
       </c>
       <c r="J21" s="4"/>
@@ -1369,25 +1343,24 @@
         <v>3</v>
       </c>
       <c r="E22" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F22" s="2">
         <v>2</v>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△汰|–潢</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△汰
-–潢</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">불</t>
+          <t xml:space="preserve">고</t>
         </is>
       </c>
       <c r="J22" s="4"/>
@@ -1409,33 +1382,23 @@
         <v>3</v>
       </c>
       <c r="E23" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F23" s="2">
         <v>2</v>
       </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|姑|仲</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-姑
-仲</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">질</t>
-        </is>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 질/릴?</t>
-        </is>
-      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I23" s="2"/>
+      <c r="J23" s="4"/>
       <c r="K23" s="2"/>
     </row>
     <row r="24">
@@ -1454,26 +1417,22 @@
         <v>3</v>
       </c>
       <c r="E24" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F24" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">러</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I24" s="2"/>
       <c r="J24" s="4"/>
       <c r="K24" s="2"/>
     </row>
@@ -1493,19 +1452,20 @@
         <v>3</v>
       </c>
       <c r="E25" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F25" s="2">
         <v>3</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I25" s="2"/>
@@ -1522,28 +1482,33 @@
         </is>
       </c>
       <c r="C26" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D26" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E26" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F26" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">△南|–</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I26" s="2"/>
+          <t xml:space="preserve">△南
+–</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">냉</t>
+        </is>
+      </c>
       <c r="J26" s="4"/>
       <c r="K26" s="2"/>
     </row>
@@ -1557,26 +1522,26 @@
         </is>
       </c>
       <c r="C27" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D27" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E27" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F27" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|△</t>
+          <t xml:space="preserve">–|南潢</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-△</t>
+          <t xml:space="preserve">–
+南潢</t>
         </is>
       </c>
       <c r="I27" s="2"/>
@@ -1599,33 +1564,28 @@
         <v>4</v>
       </c>
       <c r="E28" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F28" s="2">
         <v>1</v>
       </c>
-      <c r="G28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△|南|–</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△
-南
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△潢|–</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△潢
 –</t>
         </is>
       </c>
-      <c r="I28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">냉</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 냉/넹?</t>
-        </is>
-      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정</t>
+        </is>
+      </c>
+      <c r="J28" s="4"/>
       <c r="K28" s="2"/>
     </row>
     <row r="29">
@@ -1644,23 +1604,26 @@
         <v>4</v>
       </c>
       <c r="E29" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F29" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–|南潢</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-南潢</t>
-        </is>
-      </c>
-      <c r="I29" s="2"/>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">히</t>
+        </is>
+      </c>
       <c r="J29" s="4"/>
       <c r="K29" s="2"/>
     </row>
@@ -1680,25 +1643,25 @@
         <v>4</v>
       </c>
       <c r="E30" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F30" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△潢|–</t>
+          <t xml:space="preserve">△|–南</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△潢
-–</t>
+          <t xml:space="preserve">△
+–南</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">정</t>
+          <t xml:space="preserve">등</t>
         </is>
       </c>
       <c r="J30" s="4"/>
@@ -1720,24 +1683,25 @@
         <v>4</v>
       </c>
       <c r="E31" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F31" s="2">
         <v>2</v>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">林|仲太</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">林
+仲太</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">히</t>
+          <t xml:space="preserve">을돌</t>
         </is>
       </c>
       <c r="J31" s="4"/>
@@ -1759,107 +1723,103 @@
         <v>4</v>
       </c>
       <c r="E32" s="2">
+        <v>7</v>
+      </c>
+      <c r="F32" s="2">
+        <v>3</v>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">太</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">린</t>
+        </is>
+      </c>
+      <c r="J32" s="4"/>
+      <c r="K32" s="2"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2">
+        <v>1</v>
+      </c>
+      <c r="B33" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/옹이.png</t>
+        </is>
+      </c>
+      <c r="C33" s="2">
+        <v>4</v>
+      </c>
+      <c r="D33" s="2">
+        <v>4</v>
+      </c>
+      <c r="E33" s="2">
+        <v>8</v>
+      </c>
+      <c r="F33" s="2">
+        <v>3</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I33" s="2"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="2"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2">
+        <v>1</v>
+      </c>
+      <c r="B34" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/옹이.png</t>
+        </is>
+      </c>
+      <c r="C34" s="2">
         <v>5</v>
       </c>
-      <c r="F32" s="2">
-        <v>2</v>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="D34" s="2">
+        <v>5</v>
+      </c>
+      <c r="E34" s="2">
+        <v>1</v>
+      </c>
+      <c r="F34" s="2">
+        <v>1</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">△|–南</t>
         </is>
       </c>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 –南</t>
         </is>
       </c>
-      <c r="I32" s="2"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="2"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="2">
-        <v>1</v>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/옹이.png</t>
-        </is>
-      </c>
-      <c r="C33" s="2">
-        <v>4</v>
-      </c>
-      <c r="D33" s="2">
-        <v>4</v>
-      </c>
-      <c r="E33" s="2">
-        <v>6</v>
-      </c>
-      <c r="F33" s="2">
-        <v>2</v>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">林|仲太</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">林
-仲太</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">등을</t>
-        </is>
-      </c>
-      <c r="J33" s="4"/>
-      <c r="K33" s="2"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2">
-        <v>1</v>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/옹이.png</t>
-        </is>
-      </c>
-      <c r="C34" s="2">
-        <v>4</v>
-      </c>
-      <c r="D34" s="2">
-        <v>4</v>
-      </c>
-      <c r="E34" s="2">
-        <v>7</v>
-      </c>
-      <c r="F34" s="2">
-        <v>3</v>
-      </c>
-      <c r="G34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="H34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">太</t>
-        </is>
-      </c>
-      <c r="I34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">들</t>
-        </is>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 들/둘?</t>
-        </is>
-      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그</t>
+        </is>
+      </c>
+      <c r="J34" s="4"/>
       <c r="K34" s="2"/>
     </row>
     <row r="35">
@@ -1872,29 +1832,33 @@
         </is>
       </c>
       <c r="C35" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D35" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E35" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F35" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|△</t>
+          <t xml:space="preserve">–林|仲</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-△</t>
-        </is>
-      </c>
-      <c r="I35" s="2"/>
+          <t xml:space="preserve">–林
+仲</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사랑</t>
+        </is>
+      </c>
       <c r="J35" s="4"/>
       <c r="K35" s="2"/>
     </row>
@@ -1914,24 +1878,27 @@
         <v>5</v>
       </c>
       <c r="E36" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F36" s="2">
         <v>1</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△|南|·</t>
+          <t xml:space="preserve">△|太黃</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-南
-·</t>
-        </is>
-      </c>
-      <c r="I36" s="2"/>
+太黃</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지우</t>
+        </is>
+      </c>
       <c r="J36" s="4"/>
       <c r="K36" s="2"/>
     </row>
@@ -1951,25 +1918,25 @@
         <v>5</v>
       </c>
       <c r="E37" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F37" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–林|仲</t>
+          <t xml:space="preserve">–黃|–太</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–林
-仲</t>
+          <t xml:space="preserve">–黃
+–太</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사</t>
+          <t xml:space="preserve">려간</t>
         </is>
       </c>
       <c r="J37" s="4"/>
@@ -1991,25 +1958,25 @@
         <v>5</v>
       </c>
       <c r="E38" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F38" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△|太黃</t>
+          <t xml:space="preserve">–仲|–</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△
-太黃</t>
+          <t xml:space="preserve">–仲
+–</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">랑</t>
+          <t xml:space="preserve">다</t>
         </is>
       </c>
       <c r="J38" s="4"/>
@@ -2031,33 +1998,23 @@
         <v>5</v>
       </c>
       <c r="E39" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F39" s="2">
         <v>2</v>
       </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|黃|–</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-黃
-–</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">지</t>
-        </is>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 지/진?</t>
-        </is>
-      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I39" s="2"/>
+      <c r="J39" s="4"/>
       <c r="K39" s="2"/>
     </row>
     <row r="40">
@@ -2076,26 +2033,22 @@
         <v>5</v>
       </c>
       <c r="E40" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F40" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–太</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–太</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I40" s="2"/>
       <c r="J40" s="4"/>
       <c r="K40" s="2"/>
     </row>
@@ -2115,26 +2068,23 @@
         <v>5</v>
       </c>
       <c r="E41" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F41" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–仲</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–仲</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">러</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I41" s="2"/>
       <c r="J41" s="4"/>
       <c r="K41" s="2"/>
     </row>
@@ -2148,29 +2098,37 @@
         </is>
       </c>
       <c r="C42" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D42" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E42" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F42" s="2">
-        <v>3</v>
-      </c>
-      <c r="G42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I42" s="2"/>
-      <c r="J42" s="4"/>
+        <v>1</v>
+      </c>
+      <c r="G42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="H42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">㳞</t>
+        </is>
+      </c>
+      <c r="I42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">얼</t>
+        </is>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 열/얼? 얼마나로 봄</t>
+        </is>
+      </c>
       <c r="K42" s="2"/>
     </row>
     <row r="43">
@@ -2183,25 +2141,25 @@
         </is>
       </c>
       <c r="C43" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D43" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E43" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="F43" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I43" s="2"/>
@@ -2218,34 +2176,34 @@
         </is>
       </c>
       <c r="C44" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D44" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E44" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F44" s="2">
-        <v>3</v>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·|⌞</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·
-⌞</t>
-        </is>
-      </c>
-      <c r="I44" s="3"/>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">닫는 곡선 ")" 모양</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△汰|–潢</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△汰
+–潢</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">얼마</t>
+        </is>
+      </c>
+      <c r="J44" s="4"/>
       <c r="K44" s="2"/>
     </row>
     <row r="45">
@@ -2264,24 +2222,24 @@
         <v>6</v>
       </c>
       <c r="E45" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F45" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">얼</t>
+          <t xml:space="preserve">나</t>
         </is>
       </c>
       <c r="J45" s="4"/>
@@ -2303,22 +2261,27 @@
         <v>6</v>
       </c>
       <c r="E46" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F46" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">△|–㳞</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I46" s="2"/>
+          <t xml:space="preserve">△
+–㳞</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">달</t>
+        </is>
+      </c>
       <c r="J46" s="4"/>
       <c r="K46" s="2"/>
     </row>
@@ -2338,25 +2301,25 @@
         <v>6</v>
       </c>
       <c r="E47" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F47" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△汰|–潢</t>
+          <t xml:space="preserve">–淋|湳</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△汰
-–潢</t>
+          <t xml:space="preserve">–淋
+湳</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">얼마</t>
+          <t xml:space="preserve">려가</t>
         </is>
       </c>
       <c r="J47" s="4"/>
@@ -2378,24 +2341,25 @@
         <v>6</v>
       </c>
       <c r="E48" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F48" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–淋|–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–淋
+–</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">나</t>
+          <t xml:space="preserve">야</t>
         </is>
       </c>
       <c r="J48" s="4"/>
@@ -2417,20 +2381,20 @@
         <v>6</v>
       </c>
       <c r="E49" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F49" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△|–㳞</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△
-–㳞</t>
+          <t xml:space="preserve">–
+△</t>
         </is>
       </c>
       <c r="I49" s="2"/>
@@ -2447,31 +2411,31 @@
         </is>
       </c>
       <c r="C50" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D50" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E50" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F50" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–淋|㴌</t>
+          <t xml:space="preserve">△|湳</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–淋
-㴌</t>
+          <t xml:space="preserve">△
+湳</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">달려</t>
+          <t xml:space="preserve">이</t>
         </is>
       </c>
       <c r="J50" s="4"/>
@@ -2487,31 +2451,31 @@
         </is>
       </c>
       <c r="C51" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D51" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E51" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F51" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–淋|·</t>
+          <t xml:space="preserve">–湳|淋㳞</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–淋
-·</t>
+          <t xml:space="preserve">–湳
+淋㳞</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">가</t>
+          <t xml:space="preserve">사랑을</t>
         </is>
       </c>
       <c r="J51" s="4"/>
@@ -2527,38 +2491,34 @@
         </is>
       </c>
       <c r="C52" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D52" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E52" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F52" s="2">
-        <v>3</v>
-      </c>
-      <c r="G52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·|⌞</t>
-        </is>
-      </c>
-      <c r="H52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·
-⌞</t>
-        </is>
-      </c>
-      <c r="I52" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="J52" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">닫는 곡선 ")" 모양</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–㳞|汰潢</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–㳞
+汰潢</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">내려</t>
+        </is>
+      </c>
+      <c r="J52" s="4"/>
       <c r="K52" s="2"/>
     </row>
     <row r="53">
@@ -2577,25 +2537,25 @@
         <v>7</v>
       </c>
       <c r="E53" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F53" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△|潢</t>
+          <t xml:space="preserve">–汰|㳞</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△
-潢</t>
+          <t xml:space="preserve">–汰
+㳞</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">이</t>
+          <t xml:space="preserve">놓을</t>
         </is>
       </c>
       <c r="J53" s="4"/>
@@ -2617,25 +2577,24 @@
         <v>7</v>
       </c>
       <c r="E54" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F54" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–潢|淋㳞</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–潢
-淋㳞</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">사랑</t>
+          <t xml:space="preserve">까</t>
         </is>
       </c>
       <c r="J54" s="4"/>
@@ -2657,27 +2616,22 @@
         <v>7</v>
       </c>
       <c r="E55" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F55" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–㳞|汰潢</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–㳞
-汰潢</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">을</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I55" s="2"/>
       <c r="J55" s="4"/>
       <c r="K55" s="2"/>
     </row>
@@ -2697,27 +2651,22 @@
         <v>7</v>
       </c>
       <c r="E56" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F56" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–汰|㳞仲</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">–汰
-㳞仲</t>
-        </is>
-      </c>
-      <c r="I56" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">내</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I56" s="2"/>
       <c r="J56" s="4"/>
       <c r="K56" s="2"/>
     </row>
@@ -2737,26 +2686,23 @@
         <v>7</v>
       </c>
       <c r="E57" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F57" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">려</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I57" s="2"/>
       <c r="J57" s="4"/>
       <c r="K57" s="2"/>
     </row>
@@ -2770,28 +2716,32 @@
         </is>
       </c>
       <c r="C58" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D58" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E58" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F58" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I58" s="2"/>
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
       <c r="J58" s="4"/>
       <c r="K58" s="2"/>
     </row>
@@ -2805,25 +2755,25 @@
         </is>
       </c>
       <c r="C59" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D59" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E59" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F59" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I59" s="2"/>
@@ -2840,34 +2790,34 @@
         </is>
       </c>
       <c r="C60" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D60" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E60" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F60" s="2">
-        <v>3</v>
-      </c>
-      <c r="G60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|⌞</t>
-        </is>
-      </c>
-      <c r="H60" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-⌞</t>
-        </is>
-      </c>
-      <c r="I60" s="3"/>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">닫는 곡선 ")" 모양</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△湳|–</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△湳
+–</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디</t>
+        </is>
+      </c>
+      <c r="J60" s="4"/>
       <c r="K60" s="2"/>
     </row>
     <row r="61">
@@ -2886,24 +2836,25 @@
         <v>8</v>
       </c>
       <c r="E61" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F61" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">△湳|–</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">△湳
+–</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">어</t>
+          <t xml:space="preserve">쯤</t>
         </is>
       </c>
       <c r="J61" s="4"/>
@@ -2925,23 +2876,32 @@
         <v>8</v>
       </c>
       <c r="E62" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F62" s="2">
-        <v>1</v>
-      </c>
-      <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I62" s="2"/>
-      <c r="J62" s="4"/>
+        <v>2</v>
+      </c>
+      <c r="G62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">淋|–淋</t>
+        </is>
+      </c>
+      <c r="H62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">淋
+–淋</t>
+        </is>
+      </c>
+      <c r="I62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">음달</t>
+        </is>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 칸 음 앞에 &lt; 표시(쯤의 늘임)</t>
+        </is>
+      </c>
       <c r="K62" s="2"/>
     </row>
     <row r="63">
@@ -2960,25 +2920,25 @@
         <v>8</v>
       </c>
       <c r="E63" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F63" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△潢|–</t>
+          <t xml:space="preserve">㳞|㳞</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△潢
-–</t>
+          <t xml:space="preserve">㳞
+㳞</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">디</t>
+          <t xml:space="preserve">려</t>
         </is>
       </c>
       <c r="J63" s="4"/>
@@ -3000,32 +2960,28 @@
         <v>8</v>
       </c>
       <c r="E64" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F64" s="2">
-        <v>2</v>
-      </c>
-      <c r="G64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△潢|–</t>
-        </is>
-      </c>
-      <c r="H64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△潢
+        <v>3</v>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰㳞|–</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">汰㳞
 –</t>
         </is>
       </c>
-      <c r="I64" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">깜</t>
-        </is>
-      </c>
-      <c r="J64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 깜/감?</t>
-        </is>
-      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가야</t>
+        </is>
+      </c>
+      <c r="J64" s="4"/>
       <c r="K64" s="2"/>
     </row>
     <row r="65">
@@ -3044,27 +3000,23 @@
         <v>8</v>
       </c>
       <c r="E65" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F65" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋|–淋</t>
+          <t xml:space="preserve">–|△</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-–淋</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">음</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I65" s="2"/>
       <c r="J65" s="4"/>
       <c r="K65" s="2"/>
     </row>
@@ -3078,31 +3030,31 @@
         </is>
       </c>
       <c r="C66" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D66" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E66" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F66" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|㳞</t>
+          <t xml:space="preserve">△|–汰</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-㳞</t>
+          <t xml:space="preserve">△
+–汰</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">달</t>
+          <t xml:space="preserve">그</t>
         </is>
       </c>
       <c r="J66" s="4"/>
@@ -3118,31 +3070,31 @@
         </is>
       </c>
       <c r="C67" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D67" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E67" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="F67" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰㳞|–</t>
+          <t xml:space="preserve">㳞|汰</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰㳞
-–</t>
+          <t xml:space="preserve">㳞
+汰</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">려</t>
+          <t xml:space="preserve">리움</t>
         </is>
       </c>
       <c r="J67" s="4"/>
@@ -3158,38 +3110,33 @@
         </is>
       </c>
       <c r="C68" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D68" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E68" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F68" s="2">
-        <v>3</v>
-      </c>
-      <c r="G68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·|⌞</t>
-        </is>
-      </c>
-      <c r="H68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·
-⌞</t>
-        </is>
-      </c>
-      <c r="I68" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가야</t>
-        </is>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">닫는 곡선 ")" 모양</t>
-        </is>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">도</t>
+        </is>
+      </c>
+      <c r="J68" s="4"/>
       <c r="K68" s="2"/>
     </row>
     <row r="69">
@@ -3208,373 +3155,384 @@
         <v>9</v>
       </c>
       <c r="E69" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F69" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
+          <t xml:space="preserve">△南|南</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△南
+南</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">놓을</t>
+        </is>
+      </c>
+      <c r="J69" s="4"/>
+      <c r="K69" s="2"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2">
+        <v>1</v>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/옹이.png</t>
+        </is>
+      </c>
+      <c r="C70" s="2">
+        <v>9</v>
+      </c>
+      <c r="D70" s="2">
+        <v>9</v>
+      </c>
+      <c r="E70" s="2">
+        <v>5</v>
+      </c>
+      <c r="F70" s="2">
+        <v>2</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">까</t>
+        </is>
+      </c>
+      <c r="J70" s="4"/>
+      <c r="K70" s="2"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2">
+        <v>1</v>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/옹이.png</t>
+        </is>
+      </c>
+      <c r="C71" s="2">
+        <v>9</v>
+      </c>
+      <c r="D71" s="2">
+        <v>9</v>
+      </c>
+      <c r="E71" s="2">
+        <v>6</v>
+      </c>
+      <c r="F71" s="2">
+        <v>2</v>
+      </c>
+      <c r="G71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I71" s="3"/>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△ 작게 흘려 씀</t>
+        </is>
+      </c>
+      <c r="K71" s="2"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2">
+        <v>1</v>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/옹이.png</t>
+        </is>
+      </c>
+      <c r="C72" s="2">
+        <v>9</v>
+      </c>
+      <c r="D72" s="2">
+        <v>9</v>
+      </c>
+      <c r="E72" s="2">
+        <v>7</v>
+      </c>
+      <c r="F72" s="2">
+        <v>3</v>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="I72" s="2"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="2"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2">
+        <v>1</v>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/옹이.png</t>
+        </is>
+      </c>
+      <c r="C73" s="2">
+        <v>9</v>
+      </c>
+      <c r="D73" s="2">
+        <v>9</v>
+      </c>
+      <c r="E73" s="2">
+        <v>8</v>
+      </c>
+      <c r="F73" s="2">
+        <v>3</v>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|△</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I73" s="2"/>
+      <c r="J73" s="4"/>
+      <c r="K73" s="2"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2">
+        <v>1</v>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/옹이.png</t>
+        </is>
+      </c>
+      <c r="C74" s="2">
+        <v>10</v>
+      </c>
+      <c r="D74" s="2">
+        <v>10</v>
+      </c>
+      <c r="E74" s="2">
+        <v>1</v>
+      </c>
+      <c r="F74" s="2">
+        <v>1</v>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△南|–</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△南
+–</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">너</t>
+        </is>
+      </c>
+      <c r="J74" s="4"/>
+      <c r="K74" s="2"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2">
+        <v>1</v>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/옹이.png</t>
+        </is>
+      </c>
+      <c r="C75" s="2">
+        <v>10</v>
+      </c>
+      <c r="D75" s="2">
+        <v>10</v>
+      </c>
+      <c r="E75" s="2">
+        <v>2</v>
+      </c>
+      <c r="F75" s="2">
+        <v>1</v>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–|南</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+南</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무</t>
+        </is>
+      </c>
+      <c r="J75" s="4"/>
+      <c r="K75" s="2"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2">
+        <v>1</v>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/옹이.png</t>
+        </is>
+      </c>
+      <c r="C76" s="2">
+        <v>10</v>
+      </c>
+      <c r="D76" s="2">
+        <v>10</v>
+      </c>
+      <c r="E76" s="2">
+        <v>3</v>
+      </c>
+      <c r="F76" s="2">
+        <v>1</v>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">깊</t>
+        </is>
+      </c>
+      <c r="J76" s="4"/>
+      <c r="K76" s="2"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="2">
+        <v>1</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/옹이.png</t>
+        </is>
+      </c>
+      <c r="C77" s="2">
+        <v>10</v>
+      </c>
+      <c r="D77" s="2">
+        <v>10</v>
+      </c>
+      <c r="E77" s="2">
+        <v>4</v>
+      </c>
+      <c r="F77" s="2">
+        <v>2</v>
+      </c>
+      <c r="G77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="H77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="I77" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가사 칸 아래 경계에 &lt; 표시</t>
+        </is>
+      </c>
+      <c r="K77" s="2"/>
+    </row>
+    <row r="78">
+      <c r="A78" s="2">
+        <v>1</v>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">민요채보-1/옹이.png</t>
+        </is>
+      </c>
+      <c r="C78" s="2">
+        <v>10</v>
+      </c>
+      <c r="D78" s="2">
+        <v>10</v>
+      </c>
+      <c r="E78" s="2">
+        <v>5</v>
+      </c>
+      <c r="F78" s="2">
+        <v>2</v>
+      </c>
+      <c r="G78" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">△|–汰</t>
         </is>
       </c>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="H78" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 –汰</t>
         </is>
       </c>
-      <c r="I69" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">그</t>
-        </is>
-      </c>
-      <c r="J69" s="4"/>
-      <c r="K69" s="2"/>
-    </row>
-    <row r="70">
-      <c r="A70" s="2">
-        <v>1</v>
-      </c>
-      <c r="B70" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/옹이.png</t>
-        </is>
-      </c>
-      <c r="C70" s="2">
-        <v>9</v>
-      </c>
-      <c r="D70" s="2">
-        <v>9</v>
-      </c>
-      <c r="E70" s="2">
-        <v>2</v>
-      </c>
-      <c r="F70" s="2">
-        <v>1</v>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞汰</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞汰</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">리움</t>
-        </is>
-      </c>
-      <c r="J70" s="4"/>
-      <c r="K70" s="2"/>
-    </row>
-    <row r="71">
-      <c r="A71" s="2">
-        <v>1</v>
-      </c>
-      <c r="B71" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/옹이.png</t>
-        </is>
-      </c>
-      <c r="C71" s="2">
-        <v>9</v>
-      </c>
-      <c r="D71" s="2">
-        <v>9</v>
-      </c>
-      <c r="E71" s="2">
-        <v>3</v>
-      </c>
-      <c r="F71" s="2">
-        <v>1</v>
-      </c>
-      <c r="G71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">도</t>
-        </is>
-      </c>
-      <c r="J71" s="4"/>
-      <c r="K71" s="2"/>
-    </row>
-    <row r="72">
-      <c r="A72" s="2">
-        <v>1</v>
-      </c>
-      <c r="B72" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/옹이.png</t>
-        </is>
-      </c>
-      <c r="C72" s="2">
-        <v>9</v>
-      </c>
-      <c r="D72" s="2">
-        <v>9</v>
-      </c>
-      <c r="E72" s="2">
-        <v>4</v>
-      </c>
-      <c r="F72" s="2">
-        <v>2</v>
-      </c>
-      <c r="G72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△|南南</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△
-南南</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">놓을</t>
-        </is>
-      </c>
-      <c r="J72" s="4"/>
-      <c r="K72" s="2"/>
-    </row>
-    <row r="73">
-      <c r="A73" s="2">
-        <v>1</v>
-      </c>
-      <c r="B73" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/옹이.png</t>
-        </is>
-      </c>
-      <c r="C73" s="2">
-        <v>9</v>
-      </c>
-      <c r="D73" s="2">
-        <v>9</v>
-      </c>
-      <c r="E73" s="2">
-        <v>5</v>
-      </c>
-      <c r="F73" s="2">
-        <v>2</v>
-      </c>
-      <c r="G73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">林</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">林</t>
-        </is>
-      </c>
-      <c r="I73" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">까</t>
-        </is>
-      </c>
-      <c r="J73" s="4"/>
-      <c r="K73" s="2"/>
-    </row>
-    <row r="74">
-      <c r="A74" s="2">
-        <v>1</v>
-      </c>
-      <c r="B74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/옹이.png</t>
-        </is>
-      </c>
-      <c r="C74" s="2">
-        <v>9</v>
-      </c>
-      <c r="D74" s="2">
-        <v>9</v>
-      </c>
-      <c r="E74" s="2">
-        <v>6</v>
-      </c>
-      <c r="F74" s="2">
-        <v>2</v>
-      </c>
-      <c r="G74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|⌞</t>
-        </is>
-      </c>
-      <c r="H74" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-⌞</t>
-        </is>
-      </c>
-      <c r="I74" s="3"/>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">닫는 곡선 ")" 모양</t>
-        </is>
-      </c>
-      <c r="K74" s="2"/>
-    </row>
-    <row r="75">
-      <c r="A75" s="2">
-        <v>1</v>
-      </c>
-      <c r="B75" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/옹이.png</t>
-        </is>
-      </c>
-      <c r="C75" s="2">
-        <v>9</v>
-      </c>
-      <c r="D75" s="2">
-        <v>9</v>
-      </c>
-      <c r="E75" s="2">
-        <v>7</v>
-      </c>
-      <c r="F75" s="2">
-        <v>3</v>
-      </c>
-      <c r="G75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="H75" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·</t>
-        </is>
-      </c>
-      <c r="I75" s="2"/>
-      <c r="J75" s="4"/>
-      <c r="K75" s="2"/>
-    </row>
-    <row r="76">
-      <c r="A76" s="2">
-        <v>1</v>
-      </c>
-      <c r="B76" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/옹이.png</t>
-        </is>
-      </c>
-      <c r="C76" s="2">
-        <v>9</v>
-      </c>
-      <c r="D76" s="2">
-        <v>9</v>
-      </c>
-      <c r="E76" s="2">
-        <v>8</v>
-      </c>
-      <c r="F76" s="2">
-        <v>3</v>
-      </c>
-      <c r="G76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·|△</t>
-        </is>
-      </c>
-      <c r="H76" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">·
-△</t>
-        </is>
-      </c>
-      <c r="I76" s="2"/>
-      <c r="J76" s="4"/>
-      <c r="K76" s="2"/>
-    </row>
-    <row r="77">
-      <c r="A77" s="2">
-        <v>1</v>
-      </c>
-      <c r="B77" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/옹이.png</t>
-        </is>
-      </c>
-      <c r="C77" s="2">
-        <v>10</v>
-      </c>
-      <c r="D77" s="2">
-        <v>10</v>
-      </c>
-      <c r="E77" s="2">
-        <v>1</v>
-      </c>
-      <c r="F77" s="2">
-        <v>1</v>
-      </c>
-      <c r="G77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△|南|–</t>
-        </is>
-      </c>
-      <c r="H77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△
-南
-–</t>
-        </is>
-      </c>
-      <c r="I77" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">너</t>
-        </is>
-      </c>
-      <c r="J77" s="4"/>
-      <c r="K77" s="2"/>
-    </row>
-    <row r="78">
-      <c r="A78" s="2">
-        <v>1</v>
-      </c>
-      <c r="B78" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/옹이.png</t>
-        </is>
-      </c>
-      <c r="C78" s="2">
-        <v>10</v>
-      </c>
-      <c r="D78" s="2">
-        <v>10</v>
-      </c>
-      <c r="E78" s="2">
-        <v>2</v>
-      </c>
-      <c r="F78" s="2">
-        <v>1</v>
-      </c>
-      <c r="G78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–|南</t>
-        </is>
-      </c>
-      <c r="H78" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-南</t>
-        </is>
-      </c>
-      <c r="I78" s="2"/>
-      <c r="J78" s="4"/>
+      <c r="I78" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">옹</t>
+        </is>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">5~6정간 율명 왼쪽에 이음 곡선</t>
+        </is>
+      </c>
       <c r="K78" s="2"/>
     </row>
     <row r="79">
@@ -3593,24 +3551,25 @@
         <v>10</v>
       </c>
       <c r="E79" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F79" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">㳞|汰</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
+          <t xml:space="preserve">㳞
+汰</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">무</t>
+          <t xml:space="preserve">이가</t>
         </is>
       </c>
       <c r="J79" s="4"/>
@@ -3632,31 +3591,27 @@
         <v>10</v>
       </c>
       <c r="E80" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F80" s="2">
-        <v>2</v>
-      </c>
-      <c r="G80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="H80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="I80" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈</t>
-        </is>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사 꿈/검?</t>
-        </is>
-      </c>
+        <v>3</v>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">된</t>
+        </is>
+      </c>
+      <c r="J80" s="4"/>
       <c r="K80" s="2"/>
     </row>
     <row r="81">
@@ -3675,25 +3630,25 @@
         <v>10</v>
       </c>
       <c r="E81" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F81" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△|–汰</t>
+          <t xml:space="preserve">潢汰|–㳞</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">△
-–汰</t>
+          <t xml:space="preserve">潢汰
+–㳞</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">어</t>
+          <t xml:space="preserve">사랑때</t>
         </is>
       </c>
       <c r="J81" s="4"/>
@@ -3715,25 +3670,24 @@
         <v>10</v>
       </c>
       <c r="E82" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F82" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞|汰</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞
-汰</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">옹이가</t>
+          <t xml:space="preserve">문</t>
         </is>
       </c>
       <c r="J82" s="4"/>
@@ -3755,24 +3709,25 @@
         <v>10</v>
       </c>
       <c r="E83" s="2">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F83" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–|㳞汰</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">–
+㳞汰</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">된</t>
+          <t xml:space="preserve">에</t>
         </is>
       </c>
       <c r="J83" s="4"/>
@@ -3794,28 +3749,32 @@
         <v>10</v>
       </c>
       <c r="E84" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F84" s="2">
-        <v>3</v>
-      </c>
-      <c r="G84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰|–㳞</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢汰
-–㳞</t>
-        </is>
-      </c>
-      <c r="I84" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사랑</t>
-        </is>
-      </c>
-      <c r="J84" s="4"/>
+        <v>4</v>
+      </c>
+      <c r="G84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△黃|–潢</t>
+        </is>
+      </c>
+      <c r="H84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△黃
+–潢</t>
+        </is>
+      </c>
+      <c r="I84" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">내가</t>
+        </is>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△ 뒤 글자 氵 없는 黃으로 봄</t>
+        </is>
+      </c>
       <c r="K84" s="2"/>
     </row>
     <row r="85">
@@ -3834,151 +3793,36 @@
         <v>10</v>
       </c>
       <c r="E85" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F85" s="2">
-        <v>3</v>
-      </c>
-      <c r="G85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">淋</t>
-        </is>
-      </c>
-      <c r="I85" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">때문</t>
-        </is>
-      </c>
-      <c r="J85" s="4"/>
-      <c r="K85" s="2"/>
-    </row>
-    <row r="86">
-      <c r="A86" s="2">
-        <v>1</v>
-      </c>
-      <c r="B86" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/옹이.png</t>
-        </is>
-      </c>
-      <c r="C86" s="2">
-        <v>10</v>
-      </c>
-      <c r="D86" s="2">
-        <v>10</v>
-      </c>
-      <c r="E86" s="2">
-        <v>10</v>
-      </c>
-      <c r="F86" s="2">
         <v>4</v>
       </c>
-      <c r="G86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="I86" s="2"/>
-      <c r="J86" s="4"/>
-      <c r="K86" s="2"/>
-    </row>
-    <row r="87">
-      <c r="A87" s="2">
-        <v>1</v>
-      </c>
-      <c r="B87" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/옹이.png</t>
-        </is>
-      </c>
-      <c r="C87" s="2">
-        <v>10</v>
-      </c>
-      <c r="D87" s="2">
-        <v>10</v>
-      </c>
-      <c r="E87" s="2">
-        <v>11</v>
-      </c>
-      <c r="F87" s="2">
-        <v>4</v>
-      </c>
-      <c r="G87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞汰|△黃|–潢</t>
-        </is>
-      </c>
-      <c r="H87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞汰
-△黃
-–潢</t>
-        </is>
-      </c>
-      <c r="I87" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="J87" s="4"/>
-      <c r="K87" s="2"/>
-    </row>
-    <row r="88">
-      <c r="A88" s="2">
-        <v>1</v>
-      </c>
-      <c r="B88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">민요채보-1/옹이.png</t>
-        </is>
-      </c>
-      <c r="C88" s="2">
-        <v>10</v>
-      </c>
-      <c r="D88" s="2">
-        <v>10</v>
-      </c>
-      <c r="E88" s="2">
-        <v>12</v>
-      </c>
-      <c r="F88" s="2">
-        <v>4</v>
-      </c>
-      <c r="G88" s="3" t="inlineStr">
+      <c r="G85" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">黃汰|㳞</t>
         </is>
       </c>
-      <c r="H88" s="3" t="inlineStr">
+      <c r="H85" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">黃汰
 㳞</t>
         </is>
       </c>
-      <c r="I88" s="3" t="inlineStr">
+      <c r="I85" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">운운</t>
         </is>
       </c>
-      <c r="J88" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사·율명 모두 흐려 확실치 않음</t>
-        </is>
-      </c>
-      <c r="K88" s="2"/>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">첫 글자 氵 없는 黃으로 봄</t>
+        </is>
+      </c>
+      <c r="K85" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K88"/>
+  <autoFilter ref="A1:K85"/>
 </worksheet>
 </file>
 
@@ -4011,7 +3855,7 @@
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="82.06" customHeight="1">
+    <row r="2" ht="52.21" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4038,16 +3882,15 @@
       <c r="T2" s="20"/>
       <c r="U2" s="20"/>
     </row>
-    <row r="3" ht="82.06" customHeight="1">
+    <row r="3" ht="52.21" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△
-南
+          <t xml:space="preserve">△南
 –</t>
         </is>
       </c>
-      <c r="C3" s="29" t="inlineStr">
+      <c r="C3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">너</t>
         </is>
@@ -4058,17 +3901,17 @@
 –汰</t>
         </is>
       </c>
-      <c r="E3" s="29" t="inlineStr">
+      <c r="E3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">그</t>
         </is>
       </c>
       <c r="F3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
-        </is>
-      </c>
-      <c r="G3" s="29" t="inlineStr">
+          <t xml:space="preserve">湳</t>
+        </is>
+      </c>
+      <c r="G3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">어</t>
         </is>
@@ -4076,20 +3919,20 @@
       <c r="H3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-潢</t>
-        </is>
-      </c>
-      <c r="I3" s="29" t="inlineStr">
+湳</t>
+        </is>
+      </c>
+      <c r="I3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">이</t>
         </is>
       </c>
-      <c r="J3" s="21" t="inlineStr">
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="K3" s="29" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">얼</t>
         </is>
@@ -4097,53 +3940,55 @@
       <c r="L3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-南
+–南</t>
+        </is>
+      </c>
+      <c r="M3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">그</t>
+        </is>
+      </c>
+      <c r="N3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△南
 –</t>
         </is>
       </c>
-      <c r="M3" s="29"/>
-      <c r="N3" s="23" t="inlineStr">
+      <c r="O3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">냉</t>
+        </is>
+      </c>
+      <c r="P3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△
-南
+–潢</t>
+        </is>
+      </c>
+      <c r="Q3" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가</t>
+        </is>
+      </c>
+      <c r="R3" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△南
 –</t>
         </is>
       </c>
-      <c r="O3" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">냉</t>
-        </is>
-      </c>
-      <c r="P3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△</t>
-        </is>
-      </c>
-      <c r="Q3" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
-        </is>
-      </c>
-      <c r="R3" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△
-南
-–</t>
-        </is>
-      </c>
-      <c r="S3" s="29" t="inlineStr">
+      <c r="S3" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">사</t>
         </is>
       </c>
-      <c r="T3" s="21" t="inlineStr">
+      <c r="T3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="U3" s="29"/>
-    </row>
-    <row r="4" ht="82.06" customHeight="1">
+      <c r="U3" s="24"/>
+    </row>
+    <row r="4" ht="52.21" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4151,13 +3996,18 @@
 南</t>
         </is>
       </c>
-      <c r="C4" s="31"/>
+      <c r="C4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">무</t>
+        </is>
+      </c>
       <c r="D4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㳞汰</t>
-        </is>
-      </c>
-      <c r="E4" s="31" t="inlineStr">
+          <t xml:space="preserve">㳞
+汰</t>
+        </is>
+      </c>
+      <c r="E4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">리
 움</t>
@@ -4168,51 +4018,55 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G4" s="31"/>
+      <c r="G4" s="25"/>
       <c r="H4" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–潢
+          <t xml:space="preserve">–湳
 淋㳞</t>
         </is>
       </c>
-      <c r="I4" s="31" t="inlineStr">
+      <c r="I4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">사
+랑
+을</t>
+        </is>
+      </c>
+      <c r="J4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="K4" s="25"/>
+      <c r="L4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–林
+仲</t>
+        </is>
+      </c>
+      <c r="M4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사
 랑</t>
         </is>
       </c>
-      <c r="J4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="K4" s="31"/>
-      <c r="L4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–林
-仲</t>
-        </is>
-      </c>
-      <c r="M4" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">사</t>
-        </is>
-      </c>
       <c r="N4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 南潢</t>
         </is>
       </c>
-      <c r="O4" s="31"/>
-      <c r="P4" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–潢</t>
-        </is>
-      </c>
-      <c r="Q4" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">음</t>
+      <c r="O4" s="25"/>
+      <c r="P4" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–汰
+㳞</t>
+        </is>
+      </c>
+      <c r="Q4" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">슴
+에</t>
         </is>
       </c>
       <c r="R4" s="21" t="inlineStr">
@@ -4220,25 +4074,25 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="S4" s="31"/>
+      <c r="S4" s="25"/>
       <c r="T4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 㳞汰</t>
         </is>
       </c>
-      <c r="U4" s="31"/>
-    </row>
-    <row r="5" ht="82.06" customHeight="1">
+      <c r="U4" s="25"/>
+    </row>
+    <row r="5" ht="52.21" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="C5" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">무</t>
+      <c r="C5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">깊</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -4246,164 +4100,167 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E5" s="33" t="inlineStr">
+      <c r="E5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">도</t>
         </is>
       </c>
       <c r="F5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△湳
+–</t>
+        </is>
+      </c>
+      <c r="G5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">디</t>
+        </is>
+      </c>
+      <c r="H5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–㳞
+汰潢</t>
+        </is>
+      </c>
+      <c r="I5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">내
+려</t>
+        </is>
+      </c>
+      <c r="J5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△汰
+–潢</t>
+        </is>
+      </c>
+      <c r="K5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">얼
+마</t>
+        </is>
+      </c>
+      <c r="L5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△
+太黃</t>
+        </is>
+      </c>
+      <c r="M5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">지
+우</t>
+        </is>
+      </c>
+      <c r="N5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△潢
 –</t>
         </is>
       </c>
-      <c r="G5" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">디</t>
-        </is>
-      </c>
-      <c r="H5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–㳞
-汰潢</t>
-        </is>
-      </c>
-      <c r="I5" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">을</t>
-        </is>
-      </c>
-      <c r="J5" s="21" t="inlineStr">
+      <c r="O5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">정</t>
+        </is>
+      </c>
+      <c r="P5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△汰
 –潢</t>
         </is>
       </c>
-      <c r="K5" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">얼
-마</t>
-        </is>
-      </c>
-      <c r="L5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△
-太黃</t>
-        </is>
-      </c>
-      <c r="M5" s="33" t="inlineStr">
+      <c r="Q5" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">불
+질</t>
+        </is>
+      </c>
+      <c r="R5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△南
+–</t>
+        </is>
+      </c>
+      <c r="S5" s="26" t="inlineStr">
         <is>
           <t xml:space="preserve">랑</t>
         </is>
       </c>
-      <c r="N5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△潢
+      <c r="T5" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">潢潢
 –</t>
         </is>
       </c>
-      <c r="O5" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정</t>
-        </is>
-      </c>
-      <c r="P5" s="21" t="inlineStr">
+      <c r="U5" s="26"/>
+    </row>
+    <row r="6" ht="52.21" customHeight="1">
+      <c r="A6" s="0"/>
+      <c r="B6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="C6" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">어</t>
+        </is>
+      </c>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△南
+南</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">놓
+을</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△湳
+–</t>
+        </is>
+      </c>
+      <c r="G6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">쯤</t>
+        </is>
+      </c>
+      <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–汰
 㳞</t>
         </is>
       </c>
-      <c r="Q5" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
-        </is>
-      </c>
-      <c r="R5" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△
-南
-–</t>
-        </is>
-      </c>
-      <c r="S5" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">랑</t>
-        </is>
-      </c>
-      <c r="T5" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">潢潢
-–</t>
-        </is>
-      </c>
-      <c r="U5" s="34"/>
-    </row>
-    <row r="6" ht="82.06" customHeight="1">
-      <c r="A6" s="0"/>
-      <c r="B6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="C6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">꿈</t>
-        </is>
-      </c>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△
-南南</t>
-        </is>
-      </c>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="I6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">놓
 을</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">△潢
-–</t>
-        </is>
-      </c>
-      <c r="G6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">깜</t>
-        </is>
-      </c>
-      <c r="H6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–汰
-㳞仲</t>
-        </is>
-      </c>
-      <c r="I6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">내</t>
-        </is>
-      </c>
       <c r="J6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="K6" s="29" t="inlineStr">
+      <c r="K6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="L6" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-黃
-–</t>
-        </is>
-      </c>
-      <c r="M6" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">지</t>
+      <c r="L6" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–黃
+–太</t>
+        </is>
+      </c>
+      <c r="M6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">려
+간</t>
         </is>
       </c>
       <c r="N6" s="21" t="inlineStr">
@@ -4411,20 +4268,21 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="O6" s="29" t="inlineStr">
+      <c r="O6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">히</t>
         </is>
       </c>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">△汰
-–潢</t>
-        </is>
-      </c>
-      <c r="Q6" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">불</t>
+          <t xml:space="preserve">–南
+仲</t>
+        </is>
+      </c>
+      <c r="Q6" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">러
+놓</t>
         </is>
       </c>
       <c r="R6" s="21" t="inlineStr">
@@ -4432,7 +4290,7 @@
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="S6" s="29" t="inlineStr">
+      <c r="S6" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">에</t>
         </is>
@@ -4443,19 +4301,19 @@
 仲</t>
         </is>
       </c>
-      <c r="U6" s="29"/>
-    </row>
-    <row r="7" ht="82.06" customHeight="1">
+      <c r="U6" s="22"/>
+    </row>
+    <row r="7" ht="52.21" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△
 –汰</t>
         </is>
       </c>
-      <c r="C7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">어</t>
+      <c r="C7" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">옹</t>
         </is>
       </c>
       <c r="D7" s="21" t="inlineStr">
@@ -4463,20 +4321,21 @@
           <t xml:space="preserve">林</t>
         </is>
       </c>
-      <c r="E7" s="31" t="inlineStr">
+      <c r="E7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">까</t>
         </is>
       </c>
-      <c r="F7" s="21" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋
 –淋</t>
         </is>
       </c>
-      <c r="G7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">음</t>
+      <c r="G7" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">음
+달</t>
         </is>
       </c>
       <c r="H7" s="21" t="inlineStr">
@@ -4484,9 +4343,9 @@
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="I7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">려</t>
+      <c r="I7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">까</t>
         </is>
       </c>
       <c r="J7" s="21" t="inlineStr">
@@ -4495,15 +4354,20 @@
 –㳞</t>
         </is>
       </c>
-      <c r="K7" s="31"/>
+      <c r="K7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">달</t>
+        </is>
+      </c>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–太</t>
-        </is>
-      </c>
-      <c r="M7" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">우</t>
+          <t xml:space="preserve">–仲
+–</t>
+        </is>
+      </c>
+      <c r="M7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">다</t>
         </is>
       </c>
       <c r="N7" s="21" t="inlineStr">
@@ -4512,17 +4376,19 @@
 –南</t>
         </is>
       </c>
-      <c r="O7" s="31"/>
-      <c r="P7" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-姑
-仲</t>
-        </is>
-      </c>
-      <c r="Q7" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">질</t>
+      <c r="O7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">등</t>
+        </is>
+      </c>
+      <c r="P7" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">林</t>
+        </is>
+      </c>
+      <c r="Q7" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">고</t>
         </is>
       </c>
       <c r="R7" s="21" t="inlineStr">
@@ -4531,7 +4397,7 @@
 –林</t>
         </is>
       </c>
-      <c r="S7" s="31" t="inlineStr">
+      <c r="S7" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">불</t>
         </is>
@@ -4541,9 +4407,9 @@
           <t xml:space="preserve">㳞</t>
         </is>
       </c>
-      <c r="U7" s="31"/>
-    </row>
-    <row r="8" ht="82.06" customHeight="1">
+      <c r="U7" s="25"/>
+    </row>
+    <row r="8" ht="52.21" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4551,29 +4417,28 @@
 汰</t>
         </is>
       </c>
-      <c r="C8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">옹
-이
+      <c r="C8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">이
 가</t>
         </is>
       </c>
       <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–
-⌞</t>
-        </is>
-      </c>
-      <c r="E8" s="34"/>
+△</t>
+        </is>
+      </c>
+      <c r="E8" s="28"/>
       <c r="F8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㳞
 㳞</t>
         </is>
       </c>
-      <c r="G8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">달</t>
+      <c r="G8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">려</t>
         </is>
       </c>
       <c r="H8" s="21" t="inlineStr">
@@ -4581,77 +4446,70 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="33"/>
+      <c r="I8" s="26"/>
       <c r="J8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋
-㴌</t>
-        </is>
-      </c>
-      <c r="K8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">달
-려</t>
+湳</t>
+        </is>
+      </c>
+      <c r="K8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">려
+가</t>
         </is>
       </c>
       <c r="L8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–仲</t>
-        </is>
-      </c>
-      <c r="M8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">러</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="M8" s="26"/>
       <c r="N8" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
 仲太</t>
         </is>
       </c>
-      <c r="O8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">등
-을</t>
+      <c r="O8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">을
+돌</t>
         </is>
       </c>
       <c r="P8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林</t>
-        </is>
-      </c>
-      <c r="Q8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">러</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–</t>
+        </is>
+      </c>
+      <c r="Q8" s="26"/>
       <c r="R8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-仲</t>
-        </is>
-      </c>
-      <c r="S8" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">씨</t>
-        </is>
-      </c>
-      <c r="T8" s="21" t="inlineStr">
+          <t xml:space="preserve">–仲
+–太</t>
+        </is>
+      </c>
+      <c r="S8" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">씨
+하</t>
+        </is>
+      </c>
+      <c r="T8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="U8" s="33"/>
-    </row>
-    <row r="9" ht="82.06" customHeight="1">
+      <c r="U8" s="28"/>
+    </row>
+    <row r="9" ht="52.21" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C9" s="29" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t xml:space="preserve">된</t>
         </is>
@@ -4661,16 +4519,17 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E9" s="29"/>
+      <c r="E9" s="22"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰㳞
 –</t>
         </is>
       </c>
-      <c r="G9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">려</t>
+      <c r="G9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">가
+야</t>
         </is>
       </c>
       <c r="H9" s="21" t="inlineStr">
@@ -4678,16 +4537,16 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I9" s="29"/>
+      <c r="I9" s="22"/>
       <c r="J9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–淋
 –</t>
         </is>
       </c>
-      <c r="K9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가</t>
+      <c r="K9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">야</t>
         </is>
       </c>
       <c r="L9" s="21" t="inlineStr">
@@ -4695,15 +4554,15 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="M9" s="29"/>
-      <c r="N9" s="23" t="inlineStr">
+      <c r="M9" s="22"/>
+      <c r="N9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">太</t>
         </is>
       </c>
-      <c r="O9" s="30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">들</t>
+      <c r="O9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">린</t>
         </is>
       </c>
       <c r="P9" s="21" t="inlineStr">
@@ -4711,15 +4570,15 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="Q9" s="29"/>
+      <c r="Q9" s="22"/>
       <c r="R9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–太</t>
-        </is>
-      </c>
-      <c r="S9" s="29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">하</t>
+          <t xml:space="preserve">仲</t>
+        </is>
+      </c>
+      <c r="S9" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">나</t>
         </is>
       </c>
       <c r="T9" s="21" t="inlineStr">
@@ -4727,9 +4586,9 @@
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="U9" s="29"/>
-    </row>
-    <row r="10" ht="82.06" customHeight="1">
+      <c r="U9" s="22"/>
+    </row>
+    <row r="10" ht="52.21" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4737,10 +4596,11 @@
 –㳞</t>
         </is>
       </c>
-      <c r="C10" s="31" t="inlineStr">
+      <c r="C10" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">사
-랑</t>
+랑
+때</t>
         </is>
       </c>
       <c r="D10" s="21" t="inlineStr">
@@ -4749,181 +4609,160 @@
 △</t>
         </is>
       </c>
-      <c r="E10" s="31"/>
-      <c r="F10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-⌞</t>
-        </is>
-      </c>
-      <c r="G10" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가
-야</t>
-        </is>
-      </c>
-      <c r="H10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-⌞</t>
-        </is>
-      </c>
-      <c r="I10" s="32"/>
-      <c r="J10" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-⌞</t>
-        </is>
-      </c>
-      <c r="K10" s="32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">아</t>
-        </is>
-      </c>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="M10" s="31"/>
-      <c r="N10" s="21" t="inlineStr">
+      <c r="E10" s="25"/>
+      <c r="F10" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">–
 △</t>
         </is>
       </c>
-      <c r="O10" s="31"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="I10" s="25"/>
+      <c r="J10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="K10" s="25"/>
+      <c r="L10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="M10" s="25"/>
+      <c r="N10" s="21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="O10" s="25"/>
       <c r="P10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="Q10" s="31"/>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="Q10" s="25"/>
       <c r="R10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">仲</t>
-        </is>
-      </c>
-      <c r="S10" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">나</t>
-        </is>
-      </c>
+          <t xml:space="preserve">–
+△</t>
+        </is>
+      </c>
+      <c r="S10" s="25"/>
       <c r="T10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">⌞</t>
-        </is>
-      </c>
-      <c r="U10" s="32"/>
-    </row>
-    <row r="11" ht="82.06" customHeight="1">
+          <t xml:space="preserve">△</t>
+        </is>
+      </c>
+      <c r="U10" s="27"/>
+    </row>
+    <row r="11" ht="52.21" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">淋</t>
         </is>
       </c>
-      <c r="C11" s="33" t="inlineStr">
-        <is>
-          <t xml:space="preserve">때
-문</t>
+      <c r="C11" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">문</t>
         </is>
       </c>
       <c r="D11" s="21"/>
-      <c r="E11" s="33"/>
+      <c r="E11" s="26"/>
       <c r="F11" s="21"/>
-      <c r="G11" s="33"/>
+      <c r="G11" s="26"/>
       <c r="H11" s="21"/>
-      <c r="I11" s="33"/>
+      <c r="I11" s="26"/>
       <c r="J11" s="21"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="23" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-⌞</t>
-        </is>
-      </c>
-      <c r="M11" s="34"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="21"/>
+      <c r="M11" s="26"/>
       <c r="N11" s="21"/>
-      <c r="O11" s="33"/>
-      <c r="P11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-△</t>
-        </is>
-      </c>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">–
-△</t>
-        </is>
-      </c>
-      <c r="S11" s="33"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="21"/>
+      <c r="Q11" s="26"/>
+      <c r="R11" s="21"/>
+      <c r="S11" s="26"/>
       <c r="T11" s="21"/>
-      <c r="U11" s="33"/>
-    </row>
-    <row r="12" ht="82.06" customHeight="1">
+      <c r="U11" s="26"/>
+    </row>
+    <row r="12" ht="52.21" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–</t>
-        </is>
-      </c>
-      <c r="C12" s="29"/>
+          <t xml:space="preserve">–
+㳞汰</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">에</t>
+        </is>
+      </c>
       <c r="D12" s="21"/>
-      <c r="E12" s="29"/>
+      <c r="E12" s="22"/>
       <c r="F12" s="21"/>
-      <c r="G12" s="29"/>
+      <c r="G12" s="22"/>
       <c r="H12" s="21"/>
-      <c r="I12" s="29"/>
+      <c r="I12" s="22"/>
       <c r="J12" s="21"/>
-      <c r="K12" s="29"/>
+      <c r="K12" s="22"/>
       <c r="L12" s="21"/>
-      <c r="M12" s="29"/>
+      <c r="M12" s="22"/>
       <c r="N12" s="21"/>
-      <c r="O12" s="29"/>
+      <c r="O12" s="22"/>
       <c r="P12" s="21"/>
-      <c r="Q12" s="29"/>
+      <c r="Q12" s="22"/>
       <c r="R12" s="21"/>
-      <c r="S12" s="29"/>
+      <c r="S12" s="22"/>
       <c r="T12" s="21"/>
-      <c r="U12" s="29"/>
-    </row>
-    <row r="13" ht="82.06" customHeight="1">
+      <c r="U12" s="22"/>
+    </row>
+    <row r="13" ht="52.21" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㳞汰
-△黃
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">△黃
 –潢</t>
         </is>
       </c>
-      <c r="C13" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">에</t>
+      <c r="C13" s="27" t="inlineStr">
+        <is>
+          <t xml:space="preserve">내
+가</t>
         </is>
       </c>
       <c r="D13" s="21"/>
-      <c r="E13" s="31"/>
+      <c r="E13" s="25"/>
       <c r="F13" s="21"/>
-      <c r="G13" s="31"/>
+      <c r="G13" s="25"/>
       <c r="H13" s="21"/>
-      <c r="I13" s="31"/>
+      <c r="I13" s="25"/>
       <c r="J13" s="21"/>
-      <c r="K13" s="31"/>
+      <c r="K13" s="25"/>
       <c r="L13" s="21"/>
-      <c r="M13" s="31"/>
+      <c r="M13" s="25"/>
       <c r="N13" s="21"/>
-      <c r="O13" s="31"/>
+      <c r="O13" s="25"/>
       <c r="P13" s="21"/>
-      <c r="Q13" s="31"/>
+      <c r="Q13" s="25"/>
       <c r="R13" s="21"/>
-      <c r="S13" s="31"/>
+      <c r="S13" s="25"/>
       <c r="T13" s="21"/>
-      <c r="U13" s="31"/>
-    </row>
-    <row r="14" ht="82.06" customHeight="1">
+      <c r="U13" s="25"/>
+    </row>
+    <row r="14" ht="52.21" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -4931,30 +4770,30 @@
 㳞</t>
         </is>
       </c>
-      <c r="C14" s="34" t="inlineStr">
+      <c r="C14" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">운
 운</t>
         </is>
       </c>
       <c r="D14" s="21"/>
-      <c r="E14" s="33"/>
+      <c r="E14" s="26"/>
       <c r="F14" s="21"/>
-      <c r="G14" s="33"/>
+      <c r="G14" s="26"/>
       <c r="H14" s="21"/>
-      <c r="I14" s="33"/>
+      <c r="I14" s="26"/>
       <c r="J14" s="21"/>
-      <c r="K14" s="33"/>
+      <c r="K14" s="26"/>
       <c r="L14" s="21"/>
-      <c r="M14" s="33"/>
+      <c r="M14" s="26"/>
       <c r="N14" s="21"/>
-      <c r="O14" s="33"/>
+      <c r="O14" s="26"/>
       <c r="P14" s="21"/>
-      <c r="Q14" s="33"/>
+      <c r="Q14" s="26"/>
       <c r="R14" s="21"/>
-      <c r="S14" s="33"/>
+      <c r="S14" s="26"/>
       <c r="T14" s="21"/>
-      <c r="U14" s="33"/>
+      <c r="U14" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/옹이.xlsx
+++ b/sheets/민요/검수/옹이.xlsx
@@ -781,10 +781,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFFFFF"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
   </fills>
   <borders count="5">

--- a/sheets/민요/검수/옹이.xlsx
+++ b/sheets/민요/검수/옹이.xlsx
@@ -722,17 +722,17 @@
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
       <sz val="10"/>
-      <name val="Arial"/>
+      <name val="궁서체"/>
       <family val="0"/>
     </font>
     <font>
@@ -854,7 +854,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -900,6 +900,38 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3928,622 +3960,623 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+    <pageSetUpPr fitToPage="0"/>
   </sheetPr>
   <dimension ref="B2:Q18"/>
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="13" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="13" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="13" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="13" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="13" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="13" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="13" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="13" width="6"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16381" style="0" width="12.67"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B2" s="6" t="s">
+    <row r="1" ht="6.0" customHeight="true"/>
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
+      <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="6"/>
-      <c r="L2" s="6"/>
-      <c r="M2" s="6"/>
-      <c r="N2" s="6"/>
-      <c r="O2" s="6"/>
-      <c r="P2" s="6"/>
-      <c r="Q2" s="6"/>
-    </row>
-    <row r="3" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B3" s="7"/>
-      <c r="C3" s="8"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="7" t="s">
+      <c r="C2" s="14"/>
+      <c r="D2" s="14"/>
+      <c r="E2" s="14"/>
+      <c r="F2" s="14"/>
+      <c r="G2" s="14"/>
+      <c r="H2" s="14"/>
+      <c r="I2" s="14"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="14"/>
+      <c r="M2" s="14"/>
+      <c r="N2" s="14"/>
+      <c r="O2" s="14"/>
+      <c r="P2" s="14"/>
+      <c r="Q2" s="14"/>
+    </row>
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+      <c r="B3" s="15"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="15"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="15" t="s">
         <v>140</v>
       </c>
-      <c r="I3" s="8" t="s">
+      <c r="I3" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="16" t="s">
         <v>117</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="M3" s="8" t="s">
+      <c r="M3" s="16" t="s">
         <v>88</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="O3" s="8" t="s">
+      <c r="O3" s="16" t="s">
         <v>60</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="Q3" s="8"/>
-    </row>
-    <row r="4" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B4" s="7"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="7" t="s">
+      <c r="Q3" s="16"/>
+    </row>
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+      <c r="B4" s="15"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="15"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="15" t="s">
         <v>167</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G4" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="7" t="s">
+      <c r="I4" s="17"/>
+      <c r="J4" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="7" t="s">
+      <c r="K4" s="17"/>
+      <c r="L4" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="7" t="s">
+      <c r="M4" s="17"/>
+      <c r="N4" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="7" t="s">
+      <c r="O4" s="17"/>
+      <c r="P4" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="Q4" s="9"/>
-    </row>
-    <row r="5" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B5" s="7"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="10"/>
-      <c r="F5" s="7" t="s">
+      <c r="Q4" s="17"/>
+    </row>
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+      <c r="B5" s="15"/>
+      <c r="C5" s="18"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="G5" s="10" t="s">
+      <c r="G5" s="18" t="s">
         <v>169</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="I5" s="10" t="s">
+      <c r="I5" s="18" t="s">
         <v>144</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="J5" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="K5" s="10" t="s">
+      <c r="K5" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="L5" s="7" t="s">
+      <c r="L5" s="15" t="s">
         <v>92</v>
       </c>
-      <c r="M5" s="10" t="s">
+      <c r="M5" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="N5" s="7" t="s">
+      <c r="N5" s="15" t="s">
         <v>59</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="18" t="s">
         <v>61</v>
       </c>
-      <c r="P5" s="7" t="s">
+      <c r="P5" s="15" t="s">
         <v>50</v>
       </c>
-      <c r="Q5" s="10"/>
-    </row>
-    <row r="6" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="7"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="7" t="s">
+      <c r="Q5" s="18"/>
+    </row>
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+      <c r="B6" s="15"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="15"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="G6" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="H6" s="7" t="s">
+      <c r="H6" s="15" t="s">
         <v>143</v>
       </c>
-      <c r="I6" s="9" t="s">
+      <c r="I6" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="J6" s="7" t="s">
+      <c r="J6" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="K6" s="9" t="s">
+      <c r="K6" s="17" t="s">
         <v>71</v>
       </c>
-      <c r="L6" s="7" t="s">
+      <c r="L6" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="M6" s="9" t="s">
+      <c r="M6" s="17" t="s">
         <v>95</v>
       </c>
-      <c r="N6" s="7" t="s">
+      <c r="N6" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="O6" s="9" t="s">
+      <c r="O6" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P6" s="15" t="s">
         <v>52</v>
       </c>
-      <c r="Q6" s="9"/>
-    </row>
-    <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="7"/>
-      <c r="C7" s="8"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="7" t="s">
+      <c r="Q6" s="17"/>
+    </row>
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+      <c r="B7" s="15"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="H7" s="7" t="s">
+      <c r="H7" s="15" t="s">
         <v>147</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="16" t="s">
         <v>188</v>
       </c>
-      <c r="J7" s="7" t="s">
+      <c r="J7" s="15" t="s">
         <v>121</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="L7" s="7" t="s">
+      <c r="L7" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="M7" s="8" t="s">
+      <c r="M7" s="16" t="s">
         <v>98</v>
       </c>
-      <c r="N7" s="7" t="s">
+      <c r="N7" s="15" t="s">
         <v>65</v>
       </c>
-      <c r="O7" s="8" t="s">
+      <c r="O7" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="P7" s="7" t="s">
+      <c r="P7" s="15" t="s">
         <v>53</v>
       </c>
-      <c r="Q7" s="8"/>
-    </row>
-    <row r="8" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="7"/>
-      <c r="C8" s="10"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="10"/>
-      <c r="F8" s="7" t="s">
+      <c r="Q7" s="16"/>
+    </row>
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+      <c r="B8" s="15"/>
+      <c r="C8" s="18"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="18"/>
+      <c r="F8" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="G8" s="10" t="s">
+      <c r="G8" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="H8" s="7" t="s">
+      <c r="H8" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="I8" s="10" t="s">
+      <c r="I8" s="18" t="s">
         <v>152</v>
       </c>
-      <c r="J8" s="7" t="s">
+      <c r="J8" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="K8" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="M8" s="10" t="s">
+      <c r="M8" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="N8" s="7" t="s">
+      <c r="N8" s="15" t="s">
         <v>68</v>
       </c>
-      <c r="O8" s="10" t="s">
+      <c r="O8" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="P8" s="7" t="s">
+      <c r="P8" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="Q8" s="10"/>
-    </row>
-    <row r="9" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="7"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="10"/>
-      <c r="F9" s="7" t="s">
+      <c r="Q8" s="18"/>
+    </row>
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+      <c r="B9" s="15"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="18"/>
+      <c r="F9" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="G9" s="10" t="s">
+      <c r="G9" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="H9" s="7" t="s">
+      <c r="H9" s="15" t="s">
         <v>154</v>
       </c>
-      <c r="I9" s="10" t="s">
+      <c r="I9" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="J9" s="7" t="s">
+      <c r="J9" s="15" t="s">
         <v>127</v>
       </c>
-      <c r="K9" s="10" t="s">
+      <c r="K9" s="18" t="s">
         <v>128</v>
       </c>
-      <c r="L9" s="7" t="s">
+      <c r="L9" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="M9" s="10" t="s">
+      <c r="M9" s="18" t="s">
         <v>103</v>
       </c>
-      <c r="N9" s="7" t="s">
+      <c r="N9" s="15" t="s">
         <v>70</v>
       </c>
-      <c r="O9" s="10" t="s">
+      <c r="O9" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="P9" s="7" t="s">
+      <c r="P9" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="Q9" s="10"/>
-    </row>
-    <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="7"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="7" t="s">
+      <c r="Q9" s="18"/>
+    </row>
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+      <c r="B10" s="15"/>
+      <c r="C10" s="17"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="17"/>
+      <c r="F10" s="15" t="s">
         <v>176</v>
       </c>
-      <c r="G10" s="9" t="s">
+      <c r="G10" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="H10" s="7" t="s">
+      <c r="H10" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="7" t="s">
+      <c r="I10" s="17"/>
+      <c r="J10" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="7" t="s">
+      <c r="K10" s="17"/>
+      <c r="L10" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="M10" s="9"/>
-      <c r="N10" s="7" t="s">
+      <c r="M10" s="17"/>
+      <c r="N10" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="O10" s="9"/>
-      <c r="P10" s="7" t="s">
+      <c r="O10" s="17"/>
+      <c r="P10" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="Q10" s="9"/>
-    </row>
-    <row r="11" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="7"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="8"/>
-      <c r="F11" s="7" t="s">
+      <c r="Q10" s="17"/>
+    </row>
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+      <c r="B11" s="15"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="G11" s="8" t="s">
+      <c r="G11" s="16" t="s">
         <v>178</v>
       </c>
-      <c r="H11" s="7" t="s">
+      <c r="H11" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="I11" s="8" t="s">
+      <c r="I11" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="J11" s="7" t="s">
+      <c r="J11" s="15" t="s">
         <v>130</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="L11" s="7" t="s">
+      <c r="L11" s="15" t="s">
         <v>97</v>
       </c>
-      <c r="M11" s="8" t="s">
+      <c r="M11" s="16" t="s">
         <v>104</v>
       </c>
-      <c r="N11" s="7" t="s">
+      <c r="N11" s="15" t="s">
         <v>75</v>
       </c>
-      <c r="O11" s="8" t="s">
+      <c r="O11" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="8"/>
-    </row>
-    <row r="12" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="7"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="9"/>
-      <c r="F12" s="7" t="s">
+      <c r="P11" s="15"/>
+      <c r="Q11" s="16"/>
+    </row>
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+      <c r="B12" s="15"/>
+      <c r="C12" s="17"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="15" t="s">
         <v>48</v>
       </c>
-      <c r="G12" s="9" t="s">
+      <c r="G12" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="H12" s="7" t="s">
+      <c r="H12" s="15" t="s">
         <v>159</v>
       </c>
-      <c r="I12" s="9" t="s">
+      <c r="I12" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="J12" s="7" t="s">
+      <c r="J12" s="15" t="s">
         <v>133</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="K12" s="17" t="s">
         <v>196</v>
       </c>
-      <c r="L12" s="7" t="s">
+      <c r="L12" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="M12" s="9" t="s">
+      <c r="M12" s="17" t="s">
         <v>197</v>
       </c>
-      <c r="N12" s="7" t="s">
+      <c r="N12" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="O12" s="9" t="s">
+      <c r="O12" s="17" t="s">
         <v>198</v>
       </c>
-      <c r="P12" s="7"/>
-      <c r="Q12" s="9"/>
-    </row>
-    <row r="13" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="7"/>
-      <c r="C13" s="9"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="9"/>
-      <c r="F13" s="7" t="s">
+      <c r="P12" s="15"/>
+      <c r="Q12" s="17"/>
+    </row>
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+      <c r="B13" s="15"/>
+      <c r="C13" s="17"/>
+      <c r="D13" s="15"/>
+      <c r="E13" s="17"/>
+      <c r="F13" s="15" t="s">
         <v>180</v>
       </c>
-      <c r="G13" s="9" t="s">
+      <c r="G13" s="17" t="s">
         <v>199</v>
       </c>
-      <c r="H13" s="7" t="s">
+      <c r="H13" s="15" t="s">
         <v>94</v>
       </c>
-      <c r="I13" s="9" t="s">
+      <c r="I13" s="17" t="s">
         <v>161</v>
       </c>
-      <c r="J13" s="7" t="s">
+      <c r="J13" s="15" t="s">
         <v>136</v>
       </c>
-      <c r="K13" s="9" t="s">
+      <c r="K13" s="17" t="s">
         <v>200</v>
       </c>
-      <c r="L13" s="7" t="s">
+      <c r="L13" s="15" t="s">
         <v>109</v>
       </c>
-      <c r="M13" s="9" t="s">
+      <c r="M13" s="17" t="s">
         <v>201</v>
       </c>
-      <c r="N13" s="7" t="s">
+      <c r="N13" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="O13" s="9" t="s">
+      <c r="O13" s="17" t="s">
         <v>202</v>
       </c>
-      <c r="P13" s="7"/>
-      <c r="Q13" s="9"/>
-    </row>
-    <row r="14" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="7"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="9"/>
-      <c r="F14" s="7" t="s">
+      <c r="P13" s="15"/>
+      <c r="Q13" s="17"/>
+    </row>
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+      <c r="B14" s="15"/>
+      <c r="C14" s="17"/>
+      <c r="D14" s="15"/>
+      <c r="E14" s="17"/>
+      <c r="F14" s="15" t="s">
         <v>184</v>
       </c>
-      <c r="G14" s="9" t="s">
+      <c r="G14" s="17" t="s">
         <v>203</v>
       </c>
-      <c r="H14" s="7" t="s">
+      <c r="H14" s="15" t="s">
         <v>163</v>
       </c>
-      <c r="I14" s="9" t="s">
+      <c r="I14" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="J14" s="7" t="s">
+      <c r="J14" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="K14" s="9" t="s">
+      <c r="K14" s="17" t="s">
         <v>204</v>
       </c>
-      <c r="L14" s="7" t="s">
+      <c r="L14" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="M14" s="9" t="s">
+      <c r="M14" s="17" t="s">
         <v>205</v>
       </c>
-      <c r="N14" s="7" t="s">
+      <c r="N14" s="15" t="s">
         <v>84</v>
       </c>
-      <c r="O14" s="9" t="s">
+      <c r="O14" s="17" t="s">
         <v>206</v>
       </c>
-      <c r="P14" s="7"/>
-      <c r="Q14" s="9"/>
-    </row>
-    <row r="15" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="11"/>
-      <c r="C15" s="8"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="11" t="s">
+      <c r="P14" s="15"/>
+      <c r="Q14" s="17"/>
+    </row>
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+      <c r="B15" s="19"/>
+      <c r="C15" s="16"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="G15" s="8" t="s">
+      <c r="G15" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="H15" s="11" t="s">
+      <c r="H15" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="I15" s="8" t="s">
+      <c r="I15" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="J15" s="11" t="s">
+      <c r="J15" s="19" t="s">
         <v>45</v>
       </c>
-      <c r="K15" s="8" t="s">
+      <c r="K15" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="L15" s="11" t="s">
+      <c r="L15" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="M15" s="8" t="s">
+      <c r="M15" s="16" t="s">
         <v>116</v>
       </c>
-      <c r="N15" s="11" t="s">
+      <c r="N15" s="19" t="s">
         <v>86</v>
       </c>
-      <c r="O15" s="8" t="s">
+      <c r="O15" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="P15" s="11"/>
-      <c r="Q15" s="8"/>
-    </row>
-    <row r="16" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="7"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="9"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="9"/>
-      <c r="H16" s="7" t="s">
+      <c r="P15" s="19"/>
+      <c r="Q15" s="16"/>
+    </row>
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+      <c r="B16" s="15"/>
+      <c r="C16" s="17"/>
+      <c r="D16" s="15"/>
+      <c r="E16" s="17"/>
+      <c r="F16" s="15"/>
+      <c r="G16" s="17"/>
+      <c r="H16" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="7" t="s">
+      <c r="I16" s="17"/>
+      <c r="J16" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="7" t="s">
+      <c r="K16" s="17"/>
+      <c r="L16" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="7" t="s">
+      <c r="M16" s="17"/>
+      <c r="N16" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="O16" s="9"/>
-      <c r="P16" s="7"/>
-      <c r="Q16" s="9"/>
-    </row>
-    <row r="17" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="7"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="9"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="9"/>
-      <c r="H17" s="7" t="s">
+      <c r="O16" s="17"/>
+      <c r="P16" s="15"/>
+      <c r="Q16" s="17"/>
+    </row>
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+      <c r="B17" s="15"/>
+      <c r="C17" s="17"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="7" t="s">
+      <c r="I17" s="17"/>
+      <c r="J17" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="7" t="s">
+      <c r="K17" s="17"/>
+      <c r="L17" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="M17" s="9"/>
-      <c r="N17" s="7" t="s">
+      <c r="M17" s="17"/>
+      <c r="N17" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="O17" s="9"/>
-      <c r="P17" s="7"/>
-      <c r="Q17" s="9"/>
-    </row>
-    <row r="18" customFormat="false" ht="52.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="7"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="10"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="10"/>
-      <c r="H18" s="7" t="s">
+      <c r="O17" s="17"/>
+      <c r="P17" s="15"/>
+      <c r="Q17" s="17"/>
+    </row>
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+      <c r="B18" s="15"/>
+      <c r="C18" s="18"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="7" t="s">
+      <c r="I18" s="18"/>
+      <c r="J18" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="7" t="s">
+      <c r="K18" s="18"/>
+      <c r="L18" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="M18" s="10"/>
-      <c r="N18" s="7" t="s">
+      <c r="M18" s="18"/>
+      <c r="N18" s="15" t="s">
         <v>73</v>
       </c>
-      <c r="O18" s="10"/>
-      <c r="P18" s="7"/>
-      <c r="Q18" s="10"/>
+      <c r="O18" s="18"/>
+      <c r="P18" s="15"/>
+      <c r="Q18" s="18"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4551,7 +4584,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="61" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>

--- a/sheets/민요/검수/옹이.xlsx
+++ b/sheets/민요/검수/옹이.xlsx
@@ -3966,27 +3966,30 @@
   <sheetFormatPr defaultColWidth="8.5078125" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="12" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="13" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="12" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="13" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="12" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="13" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="12" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="13" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="12" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="13" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="12" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="13" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="12" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="13" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="12" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="12" width="10.71"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="13" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16381" style="0" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16381" min="16381" style="0" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16382" min="16382" style="0" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16383" min="16383" style="0" width="12.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16384" min="16384" style="0" width="12.67"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true"/>
-    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="68.97" customHeight="true">
+    <row r="2" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="65.57" customHeight="true">
       <c r="B2" s="14" t="s">
         <v>0</v>
       </c>
@@ -4006,7 +4009,7 @@
       <c r="P2" s="14"/>
       <c r="Q2" s="14"/>
     </row>
-    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="3" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="73.23" customHeight="true">
       <c r="B3" s="15"/>
       <c r="C3" s="16"/>
       <c r="D3" s="15"/>
@@ -4046,7 +4049,7 @@
       </c>
       <c r="Q3" s="16"/>
     </row>
-    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="4" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="73.23" customHeight="true">
       <c r="B4" s="15"/>
       <c r="C4" s="17"/>
       <c r="D4" s="15"/>
@@ -4078,7 +4081,7 @@
       </c>
       <c r="Q4" s="17"/>
     </row>
-    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="5" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="73.23" customHeight="true">
       <c r="B5" s="15"/>
       <c r="C5" s="18"/>
       <c r="D5" s="15"/>
@@ -4118,7 +4121,7 @@
       </c>
       <c r="Q5" s="18"/>
     </row>
-    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="73.23" customHeight="true">
       <c r="B6" s="15"/>
       <c r="C6" s="17"/>
       <c r="D6" s="15"/>
@@ -4158,7 +4161,7 @@
       </c>
       <c r="Q6" s="17"/>
     </row>
-    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="73.23" customHeight="true">
       <c r="B7" s="15"/>
       <c r="C7" s="16"/>
       <c r="D7" s="15"/>
@@ -4198,7 +4201,7 @@
       </c>
       <c r="Q7" s="16"/>
     </row>
-    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="73.23" customHeight="true">
       <c r="B8" s="15"/>
       <c r="C8" s="18"/>
       <c r="D8" s="15"/>
@@ -4238,7 +4241,7 @@
       </c>
       <c r="Q8" s="18"/>
     </row>
-    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="9" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="73.23" customHeight="true">
       <c r="B9" s="15"/>
       <c r="C9" s="18"/>
       <c r="D9" s="15"/>
@@ -4278,7 +4281,7 @@
       </c>
       <c r="Q9" s="18"/>
     </row>
-    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="10" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="73.23" customHeight="true">
       <c r="B10" s="15"/>
       <c r="C10" s="17"/>
       <c r="D10" s="15"/>
@@ -4310,7 +4313,7 @@
       </c>
       <c r="Q10" s="17"/>
     </row>
-    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="11" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="73.23" customHeight="true">
       <c r="B11" s="15"/>
       <c r="C11" s="16"/>
       <c r="D11" s="15"/>
@@ -4348,7 +4351,7 @@
       <c r="P11" s="15"/>
       <c r="Q11" s="16"/>
     </row>
-    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="12" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="73.23" customHeight="true">
       <c r="B12" s="15"/>
       <c r="C12" s="17"/>
       <c r="D12" s="15"/>
@@ -4386,7 +4389,7 @@
       <c r="P12" s="15"/>
       <c r="Q12" s="17"/>
     </row>
-    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="13" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="73.23" customHeight="true">
       <c r="B13" s="15"/>
       <c r="C13" s="17"/>
       <c r="D13" s="15"/>
@@ -4424,7 +4427,7 @@
       <c r="P13" s="15"/>
       <c r="Q13" s="17"/>
     </row>
-    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="14" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="73.23" customHeight="true">
       <c r="B14" s="15"/>
       <c r="C14" s="17"/>
       <c r="D14" s="15"/>
@@ -4462,7 +4465,7 @@
       <c r="P14" s="15"/>
       <c r="Q14" s="17"/>
     </row>
-    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="15" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="73.23" customHeight="true">
       <c r="B15" s="19"/>
       <c r="C15" s="16"/>
       <c r="D15" s="19"/>
@@ -4500,7 +4503,7 @@
       <c r="P15" s="19"/>
       <c r="Q15" s="16"/>
     </row>
-    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="16" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="73.23" customHeight="true">
       <c r="B16" s="15"/>
       <c r="C16" s="17"/>
       <c r="D16" s="15"/>
@@ -4526,7 +4529,7 @@
       <c r="P16" s="15"/>
       <c r="Q16" s="17"/>
     </row>
-    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="17" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="73.23" customHeight="true">
       <c r="B17" s="15"/>
       <c r="C17" s="17"/>
       <c r="D17" s="15"/>
@@ -4552,7 +4555,7 @@
       <c r="P17" s="15"/>
       <c r="Q17" s="17"/>
     </row>
-    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="77.03" customHeight="true">
+    <row r="18" customFormat="false" hidden="false" outlineLevel="0" collapsed="false" ht="73.23" customHeight="true">
       <c r="B18" s="15"/>
       <c r="C18" s="18"/>
       <c r="D18" s="15"/>
@@ -4584,7 +4587,7 @@
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="true" verticalCentered="false"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="58"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="61"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
